--- a/outputs/019f7eda-a998-7660-a73d-e43b3af67965/出行共创项目.xlsx
+++ b/outputs/019f7eda-a998-7660-a73d-e43b3af67965/出行共创项目.xlsx
@@ -8,16 +8,17 @@
     <sheet sheetId="2" name="候选决策台" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="投递汇总" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="处理报告" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="住宿候选" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="美食餐饮" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="密室候选" state="visible" r:id="rId10"/>
-    <sheet sheetId="8" name="室内休闲" state="visible" r:id="rId11"/>
-    <sheet sheetId="9" name="景点户外" state="visible" r:id="rId12"/>
-    <sheet sheetId="10" name="攻略文章" state="visible" r:id="rId13"/>
-    <sheet sheetId="11" name="两日行程" state="visible" r:id="rId14"/>
-    <sheet sheetId="12" name="预订清单" state="visible" r:id="rId15"/>
-    <sheet sheetId="13" name="项目设置" state="visible" r:id="rId16"/>
-    <sheet sheetId="14" name="项目总览" state="visible" r:id="rId17"/>
+    <sheet sheetId="5" name="团队需求" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="住宿候选" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="美食餐饮" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="密室候选" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="室内休闲" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="景点户外" state="visible" r:id="rId13"/>
+    <sheet sheetId="11" name="攻略文章" state="visible" r:id="rId14"/>
+    <sheet sheetId="12" name="两日行程" state="visible" r:id="rId15"/>
+    <sheet sheetId="13" name="预订清单" state="visible" r:id="rId16"/>
+    <sheet sheetId="14" name="项目设置" state="visible" r:id="rId17"/>
+    <sheet sheetId="15" name="项目总览" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'行程首页'!$A1:$L48</definedName>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1351" uniqueCount="551">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1326" uniqueCount="536">
   <si>
     <t>扬州旅行 · 最终方案首页</t>
   </si>
@@ -605,7 +606,13 @@
     <t>候选决策台</t>
   </si>
   <si>
-    <t>优先在这里筛选：比较价格、位置、核心规格和缺失项；黄色“人工结论 / 是否入选 / 人工备注”可直接修改。</t>
+    <t>决策的唯一修改入口：黄色列会同步到网站。真实地点的“是否入选”表示地点入选；团队需求或攻略的“是”表示线索已采纳，不会自动写入行程。</t>
+  </si>
+  <si>
+    <t>记录类型</t>
+  </si>
+  <si>
+    <t>核实状态</t>
   </si>
   <si>
     <t>大类</t>
@@ -677,6 +684,12 @@
     <t>place-001</t>
   </si>
   <si>
+    <t>真实候选</t>
+  </si>
+  <si>
+    <t>待核实</t>
+  </si>
+  <si>
     <t>园林景区</t>
   </si>
   <si>
@@ -743,6 +756,12 @@
     <t>place-006</t>
   </si>
   <si>
+    <t>团队需求</t>
+  </si>
+  <si>
+    <t>团队诉求</t>
+  </si>
+  <si>
     <t>早茶早餐</t>
   </si>
   <si>
@@ -764,7 +783,7 @@
     <t>具体门店、排队情况和人均价格需要真实链接比较</t>
   </si>
   <si>
-    <t>价格或预约等动态信息仍需核实；招牌菜；团队适合度；营业时间</t>
+    <t>价格或预约等动态信息仍需核实；原始诉求</t>
   </si>
   <si>
     <t>place-002</t>
@@ -788,6 +807,9 @@
     <t>place-3380833f-f6d0-41eb-9718-7edde5088a6d</t>
   </si>
   <si>
+    <t>攻略文章</t>
+  </si>
+  <si>
     <t>攻略</t>
   </si>
   <si>
@@ -797,9 +819,6 @@
     <t>扬州美食攻略｜10大bi吃</t>
   </si>
   <si>
-    <t>待核实</t>
-  </si>
-  <si>
     <t>扬州美食；扬州旅游攻略；扬州必吃；江浙沪周边游</t>
   </si>
   <si>
@@ -824,6 +843,9 @@
     <t>place-b34f514c-cc18-49a3-873b-8651853e07b9</t>
   </si>
   <si>
+    <t>部分核实</t>
+  </si>
+  <si>
     <t>综合攻略</t>
   </si>
   <si>
@@ -872,9 +894,6 @@
     <t>仅为占位候选，房型、噪音和停车情况都要看真实链接</t>
   </si>
   <si>
-    <t>价格或预约等动态信息仍需核实；详细地址；团队人数容量；户型；床位 / 床型；卫浴；烧烤；取消政策</t>
-  </si>
-  <si>
     <t>place-007</t>
   </si>
   <si>
@@ -905,9 +924,6 @@
     <t>暂无真实商户资料，需要补充密室链接后再比较</t>
   </si>
   <si>
-    <t>价格或预约等动态信息仍需核实；单人价格；场地规模；团队独立开场；预约要求</t>
-  </si>
-  <si>
     <t>place-74c855d3-c1e8-4eb5-b6fb-0e99a441741a</t>
   </si>
   <si>
@@ -932,7 +948,7 @@
     <t>未指定具体密室名称</t>
   </si>
   <si>
-    <t>具体密室名称；地址；营业时间；取消规则；是否可包场；主题名称；详细地址；场地规模；适合人数；团队独立开场</t>
+    <t>具体密室名称；地址；营业时间；取消规则；是否可包场</t>
   </si>
   <si>
     <t>文字</t>
@@ -992,6 +1008,9 @@
     <t>处理状态</t>
   </si>
   <si>
+    <t>生成候选数</t>
+  </si>
+  <si>
     <t>已提取信息</t>
   </si>
   <si>
@@ -1028,9 +1047,6 @@
     <t>适合6人；中恐；难度中等；有NPC互动；单人预算200元以内；位置在扬州市区；周日上午能预约</t>
   </si>
   <si>
-    <t>具体密室名称；地址；营业时间；取消规则；是否可包场</t>
-  </si>
-  <si>
     <t>团队希望找扬州市区的中恐密室，难度中等，有NPC互动，单人预算200元以内，周日上午可预约，适合6人。</t>
   </si>
   <si>
@@ -1136,6 +1152,48 @@
     <t>2026-07-20T02:02:00.000Z</t>
   </si>
   <si>
+    <t>团队成员写下的愿望和约束，只作为匹配条件；标记“采用”表示确认这条需求，不代表已经选定真实商户。</t>
+  </si>
+  <si>
+    <t>需求名称</t>
+  </si>
+  <si>
+    <t>偏好标签</t>
+  </si>
+  <si>
+    <t>目标区域</t>
+  </si>
+  <si>
+    <t>预算</t>
+  </si>
+  <si>
+    <t>期望时长</t>
+  </si>
+  <si>
+    <t>需求摘要</t>
+  </si>
+  <si>
+    <t>已表达条件</t>
+  </si>
+  <si>
+    <t>仍需匹配</t>
+  </si>
+  <si>
+    <t>是否采用</t>
+  </si>
+  <si>
+    <t>周日上午场次</t>
+  </si>
+  <si>
+    <t>住 1 晚</t>
+  </si>
+  <si>
+    <t>约 1.5 小时</t>
+  </si>
+  <si>
+    <t>约 2 小时</t>
+  </si>
+  <si>
     <t>住宿候选</t>
   </si>
   <si>
@@ -1220,51 +1278,6 @@
     <t>数据状态</t>
   </si>
   <si>
-    <t>东关街周边（具体门牌待真实链接）</t>
-  </si>
-  <si>
-    <t>日期和房源确认后计算</t>
-  </si>
-  <si>
-    <t>目标 6 人，实际容量待核实</t>
-  </si>
-  <si>
-    <t>床型与床数待核实</t>
-  </si>
-  <si>
-    <t>环境好、安静、公共空间充足</t>
-  </si>
-  <si>
-    <t>整租优先，待核实</t>
-  </si>
-  <si>
-    <t>希望可用，待核实</t>
-  </si>
-  <si>
-    <t>必须确认允许，当前未知</t>
-  </si>
-  <si>
-    <t>设备、炭火和清洁费待核实</t>
-  </si>
-  <si>
-    <t>不强求含早，周边早餐需方便</t>
-  </si>
-  <si>
-    <t>老城步行 / 打车便利优先</t>
-  </si>
-  <si>
-    <t>周五晚，具体时间待核实</t>
-  </si>
-  <si>
-    <t>周日，具体时间待核实</t>
-  </si>
-  <si>
-    <t>等待团队提交真实民宿链接</t>
-  </si>
-  <si>
-    <t>纯示例住宿，等待团队提交真实民宿</t>
-  </si>
-  <si>
     <t>美食餐饮</t>
   </si>
   <si>
@@ -1298,18 +1311,6 @@
     <t>预约要求</t>
   </si>
   <si>
-    <t>老城 / 瘦西湖周边待选</t>
-  </si>
-  <si>
-    <t>早餐时段待核实</t>
-  </si>
-  <si>
-    <t>核对能否提前排号或预约</t>
-  </si>
-  <si>
-    <t>流程示例，等待餐厅链接核实</t>
-  </si>
-  <si>
     <t>密室候选</t>
   </si>
   <si>
@@ -1361,54 +1362,6 @@
     <t>换装</t>
   </si>
   <si>
-    <t>中恐</t>
-  </si>
-  <si>
-    <t>中等</t>
-  </si>
-  <si>
-    <t>周日上午场次</t>
-  </si>
-  <si>
-    <t>周日上午可预约</t>
-  </si>
-  <si>
-    <t>明确预算和恐怖程度；有NPC互动需求；时间明确</t>
-  </si>
-  <si>
-    <t>未指定具体密室名称；未确认是否有6人场次</t>
-  </si>
-  <si>
-    <t>团队文字诉求：适合6人，中恐，难度中等，有NPC互动，单人预算200元以内，扬州市区，周日上午能预约。</t>
-  </si>
-  <si>
-    <t>团队文字需求，具体商户待匹配</t>
-  </si>
-  <si>
-    <t>六人密室主题待选</t>
-  </si>
-  <si>
-    <t>扬州市区待选</t>
-  </si>
-  <si>
-    <t>团队确认</t>
-  </si>
-  <si>
-    <t>中等优先</t>
-  </si>
-  <si>
-    <t>6 人</t>
-  </si>
-  <si>
-    <t>约 2 小时</t>
-  </si>
-  <si>
-    <t>通常需预约，具体规则待真实链接</t>
-  </si>
-  <si>
-    <t>空位候选，等待真实密室链接</t>
-  </si>
-  <si>
     <t>室内休闲</t>
   </si>
   <si>
@@ -1475,10 +1428,7 @@
     <t>流程示例，等待官方信息核实</t>
   </si>
   <si>
-    <t>攻略文章</t>
-  </si>
-  <si>
-    <t>攻略完整明细：摘要、避坑、证据、缺失信息和团队意见；黄色列可直接修改。</t>
+    <t>攻略完整明细：摘要、避坑、证据和缺失信息；决策状态请统一到“候选决策台”修改。</t>
   </si>
   <si>
     <t>标题</t>
@@ -1649,22 +1599,28 @@
     <t>候选资料</t>
   </si>
   <si>
-    <t>含住宿、活动、餐饮、景点和攻略</t>
+    <t>真实候选 4 · 团队需求 4 · 攻略 3</t>
   </si>
   <si>
     <t>分类明细</t>
   </si>
   <si>
-    <t>住宿 1 · 餐饮 1 · 密室 2 · 休闲娱乐 0 · 景点 4 · 攻略 3</t>
-  </si>
-  <si>
-    <t>查看对应分类工作表</t>
-  </si>
-  <si>
-    <t>已入选候选</t>
-  </si>
-  <si>
-    <t>用于当前行程草案</t>
+    <t>住宿 0 · 餐饮 0 · 密室 0 · 休闲娱乐 0 · 景点 4 · 攻略 3</t>
+  </si>
+  <si>
+    <t>团队诉求请查看“团队需求”工作表</t>
+  </si>
+  <si>
+    <t>已入选地点</t>
+  </si>
+  <si>
+    <t>真实地点，可用于当前行程草案</t>
+  </si>
+  <si>
+    <t>已采纳需求 / 攻略</t>
+  </si>
+  <si>
+    <t>筛选条件或来源线索，不会自动写入行程</t>
   </si>
   <si>
     <t>待确认预订</t>
@@ -1887,7 +1843,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1957,14 +1913,14 @@
     <xf numFmtId="0" fontId="11" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="9" fontId="16" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1984,21 +1940,15 @@
     <xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="15" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="18" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3547,6 +3497,605 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:AH7"/>
+  <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="18" style="35" customWidth="1"/>
+    <col min="8" max="8" width="30" customWidth="1"/>
+    <col min="9" max="9" width="16" customWidth="1"/>
+    <col min="10" max="13" width="18" customWidth="1"/>
+    <col min="14" max="14" width="30" customWidth="1"/>
+    <col min="15" max="16" width="16" customWidth="1"/>
+    <col min="17" max="18" width="18" customWidth="1"/>
+    <col min="19" max="19" width="16" style="18" customWidth="1"/>
+    <col min="20" max="20" width="18" style="17" customWidth="1"/>
+    <col min="21" max="22" width="30" customWidth="1"/>
+    <col min="23" max="28" width="18" customWidth="1"/>
+    <col min="29" max="29" width="30" customWidth="1"/>
+    <col min="30" max="30" width="18" customWidth="1"/>
+    <col min="31" max="31" width="16" customWidth="1"/>
+    <col min="32" max="32" width="38" customWidth="1"/>
+    <col min="33" max="33" width="36" customWidth="1"/>
+    <col min="34" max="34" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
+        <v>455</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="19"/>
+      <c r="S1" s="19"/>
+      <c r="T1" s="19"/>
+      <c r="U1" s="19"/>
+      <c r="V1" s="19"/>
+      <c r="W1" s="19"/>
+      <c r="X1" s="19"/>
+      <c r="Y1" s="19"/>
+      <c r="Z1" s="19"/>
+      <c r="AA1" s="19"/>
+      <c r="AB1" s="19"/>
+      <c r="AC1" s="19"/>
+      <c r="AD1" s="19"/>
+      <c r="AE1" s="19"/>
+      <c r="AF1" s="19"/>
+      <c r="AG1" s="19"/>
+      <c r="AH1" s="19"/>
+    </row>
+    <row r="2" ht="34" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A2" s="20" t="s">
+        <v>456</v>
+      </c>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
+      <c r="R2" s="20"/>
+      <c r="S2" s="20"/>
+      <c r="T2" s="20"/>
+      <c r="U2" s="20"/>
+      <c r="V2" s="20"/>
+      <c r="W2" s="20"/>
+      <c r="X2" s="20"/>
+      <c r="Y2" s="20"/>
+      <c r="Z2" s="20"/>
+      <c r="AA2" s="20"/>
+      <c r="AB2" s="20"/>
+      <c r="AC2" s="20"/>
+      <c r="AD2" s="20"/>
+      <c r="AE2" s="20"/>
+      <c r="AF2" s="20"/>
+      <c r="AG2" s="20"/>
+      <c r="AH2" s="20"/>
+    </row>
+    <row r="3" ht="34" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A3" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>197</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>390</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="36" t="s">
+        <v>457</v>
+      </c>
+      <c r="H3" s="21" t="s">
+        <v>458</v>
+      </c>
+      <c r="I3" s="21" t="s">
+        <v>425</v>
+      </c>
+      <c r="J3" s="21" t="s">
+        <v>459</v>
+      </c>
+      <c r="K3" s="21" t="s">
+        <v>460</v>
+      </c>
+      <c r="L3" s="21" t="s">
+        <v>461</v>
+      </c>
+      <c r="M3" s="21" t="s">
+        <v>426</v>
+      </c>
+      <c r="N3" s="21" t="s">
+        <v>408</v>
+      </c>
+      <c r="O3" s="21" t="s">
+        <v>405</v>
+      </c>
+      <c r="P3" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q3" s="21" t="s">
+        <v>462</v>
+      </c>
+      <c r="R3" s="21" t="s">
+        <v>463</v>
+      </c>
+      <c r="S3" s="23" t="s">
+        <v>412</v>
+      </c>
+      <c r="T3" s="22" t="s">
+        <v>204</v>
+      </c>
+      <c r="U3" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="V3" s="21" t="s">
+        <v>413</v>
+      </c>
+      <c r="W3" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="X3" s="21" t="s">
+        <v>208</v>
+      </c>
+      <c r="Y3" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="Z3" s="21" t="s">
+        <v>414</v>
+      </c>
+      <c r="AA3" s="21" t="s">
+        <v>210</v>
+      </c>
+      <c r="AB3" s="21" t="s">
+        <v>211</v>
+      </c>
+      <c r="AC3" s="21" t="s">
+        <v>212</v>
+      </c>
+      <c r="AD3" s="21" t="s">
+        <v>213</v>
+      </c>
+      <c r="AE3" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AF3" s="21" t="s">
+        <v>215</v>
+      </c>
+      <c r="AG3" s="21" t="s">
+        <v>216</v>
+      </c>
+      <c r="AH3" s="21" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A4" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="B4" s="34" t="s">
+        <v>221</v>
+      </c>
+      <c r="C4" s="34" t="s">
+        <v>220</v>
+      </c>
+      <c r="D4" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="E4" s="34" t="s">
+        <v>222</v>
+      </c>
+      <c r="F4" s="34" t="s">
+        <v>222</v>
+      </c>
+      <c r="G4" s="37"/>
+      <c r="H4" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="I4" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="J4" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="K4" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="L4" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="M4" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="N4" s="24" t="s">
+        <v>219</v>
+      </c>
+      <c r="O4" s="24" t="s">
+        <v>219</v>
+      </c>
+      <c r="P4" s="24" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q4" s="24" t="s">
+        <v>224</v>
+      </c>
+      <c r="R4" s="24" t="s">
+        <v>225</v>
+      </c>
+      <c r="S4" s="27">
+        <v>4.8</v>
+      </c>
+      <c r="T4" s="26">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="U4" s="24" t="s">
+        <v>226</v>
+      </c>
+      <c r="V4" s="24" t="s">
+        <v>219</v>
+      </c>
+      <c r="W4" s="24">
+        <v>0</v>
+      </c>
+      <c r="X4" s="24">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="24">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="24"/>
+      <c r="AA4" s="24" t="s">
+        <v>227</v>
+      </c>
+      <c r="AB4" s="24" t="s">
+        <v>228</v>
+      </c>
+      <c r="AC4" s="24"/>
+      <c r="AD4" s="24"/>
+      <c r="AE4" s="24" t="s">
+        <v>229</v>
+      </c>
+      <c r="AF4" s="24"/>
+      <c r="AG4" s="24"/>
+      <c r="AH4" s="24" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>252</v>
+      </c>
+      <c r="B5" s="34" t="s">
+        <v>254</v>
+      </c>
+      <c r="C5" s="34" t="s">
+        <v>253</v>
+      </c>
+      <c r="D5" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="E5" s="34" t="s">
+        <v>255</v>
+      </c>
+      <c r="F5" s="34" t="s">
+        <v>255</v>
+      </c>
+      <c r="G5" s="37">
+        <v>0</v>
+      </c>
+      <c r="H5" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="I5" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="J5" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="K5" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="L5" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="M5" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="N5" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="O5" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="P5" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q5" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="R5" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="S5" s="30">
+        <v>4.3</v>
+      </c>
+      <c r="T5" s="29">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="U5" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="V5" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="W5" s="14">
+        <v>0</v>
+      </c>
+      <c r="X5" s="14">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="14">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="14"/>
+      <c r="AA5" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="AB5" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="AC5" s="14"/>
+      <c r="AD5" s="14"/>
+      <c r="AE5" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="AF5" s="14"/>
+      <c r="AG5" s="14"/>
+      <c r="AH5" s="14" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A6" s="24" t="s">
+        <v>237</v>
+      </c>
+      <c r="B6" s="34" t="s">
+        <v>238</v>
+      </c>
+      <c r="C6" s="34" t="s">
+        <v>220</v>
+      </c>
+      <c r="D6" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="E6" s="34" t="s">
+        <v>110</v>
+      </c>
+      <c r="F6" s="34" t="s">
+        <v>110</v>
+      </c>
+      <c r="G6" s="37"/>
+      <c r="H6" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="I6" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="J6" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="K6" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="L6" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="M6" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="N6" s="24" t="s">
+        <v>219</v>
+      </c>
+      <c r="O6" s="24" t="s">
+        <v>219</v>
+      </c>
+      <c r="P6" s="24" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q6" s="24" t="s">
+        <v>239</v>
+      </c>
+      <c r="R6" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="S6" s="27">
+        <v>4.6</v>
+      </c>
+      <c r="T6" s="26">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="U6" s="24" t="s">
+        <v>226</v>
+      </c>
+      <c r="V6" s="24" t="s">
+        <v>219</v>
+      </c>
+      <c r="W6" s="24">
+        <v>0</v>
+      </c>
+      <c r="X6" s="24">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="24">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="24"/>
+      <c r="AA6" s="24" t="s">
+        <v>227</v>
+      </c>
+      <c r="AB6" s="24" t="s">
+        <v>228</v>
+      </c>
+      <c r="AC6" s="24"/>
+      <c r="AD6" s="24"/>
+      <c r="AE6" s="24" t="s">
+        <v>229</v>
+      </c>
+      <c r="AF6" s="24"/>
+      <c r="AG6" s="24"/>
+      <c r="AH6" s="24" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>230</v>
+      </c>
+      <c r="B7" s="34" t="s">
+        <v>142</v>
+      </c>
+      <c r="C7" s="34" t="s">
+        <v>141</v>
+      </c>
+      <c r="D7" s="34" t="s">
+        <v>233</v>
+      </c>
+      <c r="E7" s="34" t="s">
+        <v>231</v>
+      </c>
+      <c r="F7" s="34" t="s">
+        <v>231</v>
+      </c>
+      <c r="G7" s="37">
+        <v>0</v>
+      </c>
+      <c r="H7" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="I7" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="J7" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="K7" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="L7" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="M7" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="N7" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="O7" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="P7" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q7" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="R7" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="S7" s="30">
+        <v>4.7</v>
+      </c>
+      <c r="T7" s="29">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="U7" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="V7" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="W7" s="14">
+        <v>0</v>
+      </c>
+      <c r="X7" s="14">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="14">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="14"/>
+      <c r="AA7" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="AB7" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="AC7" s="14"/>
+      <c r="AD7" s="14"/>
+      <c r="AE7" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="AF7" s="14"/>
+      <c r="AG7" s="14"/>
+      <c r="AH7" s="14" t="s">
+        <v>465</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:AH7"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:AH1"/>
+    <mergeCell ref="A2:AH2"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L扬州出行共创&amp;R第 &amp;P / &amp;N 页</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:W6"/>
   <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
@@ -3569,7 +4118,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>482</v>
+        <v>259</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -3596,7 +4145,7 @@
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
-        <v>483</v>
+        <v>466</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
@@ -3626,105 +4175,105 @@
         <v>155</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>484</v>
+        <v>467</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>485</v>
+        <v>468</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>486</v>
+        <v>469</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="J3" s="22" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K3" s="21" t="s">
-        <v>394</v>
+        <v>413</v>
       </c>
       <c r="L3" s="21" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="M3" s="21" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="N3" s="21" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="O3" s="21" t="s">
-        <v>395</v>
+        <v>414</v>
       </c>
       <c r="P3" s="21" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q3" s="21" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="R3" s="21" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="S3" s="21" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="T3" s="21" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="U3" s="21" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="V3" s="21" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="W3" s="21" t="s">
-        <v>396</v>
+        <v>415</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
-        <v>252</v>
-      </c>
-      <c r="B4" s="36" t="s">
-        <v>255</v>
-      </c>
-      <c r="C4" s="36" t="s">
-        <v>254</v>
-      </c>
-      <c r="D4" s="36" t="s">
-        <v>253</v>
-      </c>
-      <c r="E4" s="36" t="s">
+        <v>258</v>
+      </c>
+      <c r="B4" s="34" t="s">
+        <v>262</v>
+      </c>
+      <c r="C4" s="34" t="s">
+        <v>261</v>
+      </c>
+      <c r="D4" s="34" t="s">
+        <v>260</v>
+      </c>
+      <c r="E4" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="24" t="s">
-        <v>343</v>
-      </c>
-      <c r="G4" s="24" t="s">
-        <v>259</v>
+      <c r="F4" s="34" t="s">
+        <v>348</v>
+      </c>
+      <c r="G4" s="34" t="s">
+        <v>265</v>
       </c>
       <c r="H4" s="24" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="I4" s="24" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="J4" s="31">
         <v>1</v>
       </c>
-      <c r="K4" s="24" t="s">
-        <v>256</v>
+      <c r="K4" s="34" t="s">
+        <v>219</v>
       </c>
       <c r="L4" s="24">
         <v>0</v>
@@ -3736,58 +4285,58 @@
         <v>0</v>
       </c>
       <c r="O4" s="24"/>
-      <c r="P4" s="27" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q4" s="27" t="s">
-        <v>262</v>
-      </c>
-      <c r="R4" s="28"/>
+      <c r="P4" s="24" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q4" s="24" t="s">
+        <v>268</v>
+      </c>
+      <c r="R4" s="24"/>
       <c r="S4" s="24"/>
       <c r="T4" s="24" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="U4" s="24"/>
       <c r="V4" s="24" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="W4" s="24" t="s">
-        <v>256</v>
+        <v>219</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>264</v>
-      </c>
-      <c r="B5" s="36" t="s">
-        <v>266</v>
-      </c>
-      <c r="C5" s="36" t="s">
-        <v>265</v>
-      </c>
-      <c r="D5" s="36" t="s">
-        <v>253</v>
-      </c>
-      <c r="E5" s="36" t="s">
-        <v>267</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>350</v>
-      </c>
-      <c r="G5" s="14" t="s">
         <v>270</v>
       </c>
+      <c r="B5" s="34" t="s">
+        <v>273</v>
+      </c>
+      <c r="C5" s="34" t="s">
+        <v>272</v>
+      </c>
+      <c r="D5" s="34" t="s">
+        <v>260</v>
+      </c>
+      <c r="E5" s="34" t="s">
+        <v>274</v>
+      </c>
+      <c r="F5" s="34" t="s">
+        <v>355</v>
+      </c>
+      <c r="G5" s="34" t="s">
+        <v>277</v>
+      </c>
       <c r="H5" s="14" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="J5" s="31">
         <v>0.75</v>
       </c>
-      <c r="K5" s="14" t="s">
-        <v>256</v>
+      <c r="K5" s="34" t="s">
+        <v>219</v>
       </c>
       <c r="L5" s="14">
         <v>0</v>
@@ -3799,58 +4348,58 @@
         <v>0</v>
       </c>
       <c r="O5" s="14"/>
-      <c r="P5" s="27" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q5" s="27" t="s">
-        <v>262</v>
-      </c>
-      <c r="R5" s="28"/>
+      <c r="P5" s="14" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q5" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="R5" s="14"/>
       <c r="S5" s="14"/>
       <c r="T5" s="14" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="U5" s="14"/>
       <c r="V5" s="14" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="W5" s="14" t="s">
-        <v>487</v>
+        <v>470</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
-        <v>304</v>
-      </c>
-      <c r="B6" s="36" t="s">
-        <v>306</v>
-      </c>
-      <c r="C6" s="36" t="s">
-        <v>305</v>
-      </c>
-      <c r="D6" s="36" t="s">
-        <v>253</v>
-      </c>
-      <c r="E6" s="36" t="s">
+        <v>309</v>
+      </c>
+      <c r="B6" s="34" t="s">
+        <v>311</v>
+      </c>
+      <c r="C6" s="34" t="s">
+        <v>310</v>
+      </c>
+      <c r="D6" s="34" t="s">
+        <v>260</v>
+      </c>
+      <c r="E6" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="24" t="s">
-        <v>355</v>
-      </c>
-      <c r="G6" s="24" t="s">
-        <v>310</v>
+      <c r="F6" s="34" t="s">
+        <v>360</v>
+      </c>
+      <c r="G6" s="34" t="s">
+        <v>315</v>
       </c>
       <c r="H6" s="24" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="I6" s="24" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="J6" s="31">
         <v>1</v>
       </c>
-      <c r="K6" s="24" t="s">
-        <v>256</v>
+      <c r="K6" s="34" t="s">
+        <v>219</v>
       </c>
       <c r="L6" s="24">
         <v>0</v>
@@ -3862,23 +4411,23 @@
         <v>0</v>
       </c>
       <c r="O6" s="24"/>
-      <c r="P6" s="27" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q6" s="27" t="s">
-        <v>262</v>
-      </c>
-      <c r="R6" s="28"/>
+      <c r="P6" s="24" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q6" s="24" t="s">
+        <v>268</v>
+      </c>
+      <c r="R6" s="24"/>
       <c r="S6" s="24"/>
       <c r="T6" s="24" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="U6" s="24"/>
       <c r="V6" s="24" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="W6" s="24" t="s">
-        <v>488</v>
+        <v>471</v>
       </c>
     </row>
   </sheetData>
@@ -3887,14 +4436,6 @@
     <mergeCell ref="A1:W1"/>
     <mergeCell ref="A2:W2"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation type="list" sqref="P4:P6">
-      <formula1>"待比较,备选,拟定,淘汰"</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="Q4:Q6">
-      <formula1>"是,否"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
@@ -3903,7 +4444,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -3923,7 +4464,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="32" t="s">
-        <v>489</v>
+        <v>472</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
@@ -3940,7 +4481,7 @@
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="33" t="s">
-        <v>490</v>
+        <v>473</v>
       </c>
       <c r="B2" s="33"/>
       <c r="C2" s="33"/>
@@ -3969,10 +4510,10 @@
         <v>61</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>491</v>
+        <v>474</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>492</v>
+        <v>475</v>
       </c>
       <c r="G3" s="21" t="s">
         <v>31</v>
@@ -3981,16 +4522,16 @@
         <v>65</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>493</v>
+        <v>476</v>
       </c>
       <c r="J3" s="21" t="s">
         <v>67</v>
       </c>
       <c r="K3" s="21" t="s">
-        <v>479</v>
+        <v>463</v>
       </c>
       <c r="L3" s="21" t="s">
-        <v>494</v>
+        <v>477</v>
       </c>
       <c r="M3" s="21" t="s">
         <v>68</v>
@@ -4417,7 +4958,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -4433,7 +4974,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="32" t="s">
-        <v>495</v>
+        <v>478</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
@@ -4445,7 +4986,7 @@
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="33" t="s">
-        <v>496</v>
+        <v>479</v>
       </c>
       <c r="B2" s="33"/>
       <c r="C2" s="33"/>
@@ -4651,7 +5192,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -4665,27 +5206,27 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="32" t="s">
-        <v>497</v>
+        <v>480</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="33" t="s">
-        <v>498</v>
+        <v>481</v>
       </c>
       <c r="B2" s="33"/>
       <c r="C2" s="33"/>
     </row>
     <row r="3" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
-        <v>499</v>
+        <v>482</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>500</v>
+        <v>483</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>501</v>
+        <v>484</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -4696,18 +5237,18 @@
         <v>9</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>502</v>
+        <v>485</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>503</v>
+        <v>486</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>16</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>504</v>
+        <v>487</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -4718,7 +5259,7 @@
         <v>6</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>505</v>
+        <v>488</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -4729,40 +5270,40 @@
         <v>2</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>506</v>
+        <v>489</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="24" t="s">
-        <v>507</v>
+        <v>490</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>508</v>
+        <v>491</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>509</v>
+        <v>492</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>510</v>
+        <v>493</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>511</v>
+        <v>494</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="24" t="s">
-        <v>512</v>
+        <v>495</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>513</v>
+        <v>496</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>514</v>
+        <v>497</v>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -4770,54 +5311,54 @@
         <v>91</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>515</v>
+        <v>498</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>516</v>
+        <v>499</v>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="24" t="s">
-        <v>517</v>
+        <v>500</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>518</v>
+        <v>501</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>519</v>
+        <v>502</v>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>520</v>
+        <v>503</v>
       </c>
       <c r="B13" s="14" t="s">
         <v>130</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>521</v>
+        <v>504</v>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="24" t="s">
-        <v>522</v>
+        <v>505</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>523</v>
+        <v>506</v>
       </c>
     </row>
     <row r="15" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
-        <v>524</v>
+        <v>507</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>525</v>
+        <v>508</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>526</v>
+        <v>509</v>
       </c>
     </row>
   </sheetData>
@@ -4834,12 +5375,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="18" customWidth="1"/>
@@ -4848,130 +5389,141 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="32" t="s">
-        <v>527</v>
+        <v>510</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="33" t="s">
-        <v>528</v>
+        <v>511</v>
       </c>
       <c r="B2" s="33"/>
       <c r="C2" s="33"/>
     </row>
     <row r="3" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
-        <v>529</v>
+        <v>512</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>530</v>
+        <v>513</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>501</v>
+        <v>484</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
-        <v>531</v>
+        <v>514</v>
       </c>
       <c r="B4" s="24" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>532</v>
+        <v>515</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>533</v>
+        <v>516</v>
       </c>
       <c r="B5" s="14">
         <v>4</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>534</v>
+        <v>517</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
-        <v>535</v>
+        <v>518</v>
       </c>
       <c r="B6" s="24">
         <v>4</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>536</v>
+        <v>519</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>537</v>
+        <v>520</v>
       </c>
       <c r="B7" s="14">
         <v>0</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>538</v>
+        <v>521</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="24" t="s">
-        <v>539</v>
+        <v>522</v>
       </c>
       <c r="B8" s="24">
         <v>11</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>540</v>
+        <v>523</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>541</v>
+        <v>524</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>542</v>
+        <v>525</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>543</v>
+        <v>526</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="24" t="s">
-        <v>544</v>
+        <v>527</v>
       </c>
       <c r="B10" s="24">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>545</v>
+        <v>528</v>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>546</v>
+        <v>529</v>
       </c>
       <c r="B11" s="14">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>547</v>
+        <v>530</v>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="24" t="s">
-        <v>548</v>
-      </c>
-      <c r="B12" s="24" t="s">
-        <v>549</v>
+        <v>531</v>
+      </c>
+      <c r="B12" s="24">
+        <v>6</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>550</v>
+        <v>532</v>
+      </c>
+    </row>
+    <row r="13" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="14" t="s">
+        <v>533</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>534</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>535</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:C12"/>
+  <autoFilter ref="A3:C13"/>
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
@@ -4990,31 +5542,32 @@
     <tabColor rgb="D9703E"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:W14"/>
+  <dimension ref="A1:Y14"/>
   <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="24" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="30" customWidth="1"/>
-    <col min="8" max="10" width="24" customWidth="1"/>
-    <col min="11" max="11" width="13" style="17" customWidth="1"/>
-    <col min="12" max="12" width="28" customWidth="1"/>
-    <col min="13" max="13" width="12" style="18" customWidth="1"/>
-    <col min="14" max="16" width="10" customWidth="1"/>
-    <col min="17" max="17" width="12" customWidth="1"/>
-    <col min="18" max="18" width="10" customWidth="1"/>
-    <col min="19" max="19" width="28" customWidth="1"/>
-    <col min="20" max="20" width="22" customWidth="1"/>
-    <col min="21" max="21" width="12" customWidth="1"/>
-    <col min="22" max="22" width="38" customWidth="1"/>
-    <col min="23" max="23" width="36" customWidth="1"/>
+    <col min="2" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="24" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="30" customWidth="1"/>
+    <col min="10" max="12" width="24" customWidth="1"/>
+    <col min="13" max="13" width="13" style="17" customWidth="1"/>
+    <col min="14" max="14" width="28" customWidth="1"/>
+    <col min="15" max="15" width="12" style="18" customWidth="1"/>
+    <col min="16" max="18" width="10" customWidth="1"/>
+    <col min="19" max="19" width="12" customWidth="1"/>
+    <col min="20" max="20" width="10" customWidth="1"/>
+    <col min="21" max="21" width="28" customWidth="1"/>
+    <col min="22" max="22" width="22" customWidth="1"/>
+    <col min="23" max="23" width="12" customWidth="1"/>
+    <col min="24" max="24" width="38" customWidth="1"/>
+    <col min="25" max="25" width="36" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1" ht="36" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
         <v>191</v>
       </c>
@@ -5040,8 +5593,10 @@
       <c r="U1" s="19"/>
       <c r="V1" s="19"/>
       <c r="W1" s="19"/>
-    </row>
-    <row r="2" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X1" s="19"/>
+      <c r="Y1" s="19"/>
+    </row>
+    <row r="2" ht="34" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
         <v>192</v>
       </c>
@@ -5067,8 +5622,10 @@
       <c r="U2" s="20"/>
       <c r="V2" s="20"/>
       <c r="W2" s="20"/>
-    </row>
-    <row r="3" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X2" s="20"/>
+      <c r="Y2" s="20"/>
+    </row>
+    <row r="3" ht="34" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
         <v>155</v>
       </c>
@@ -5099,19 +5656,19 @@
       <c r="J3" s="21" t="s">
         <v>201</v>
       </c>
-      <c r="K3" s="22" t="s">
+      <c r="K3" s="21" t="s">
         <v>202</v>
       </c>
       <c r="L3" s="21" t="s">
         <v>203</v>
       </c>
-      <c r="M3" s="23" t="s">
+      <c r="M3" s="22" t="s">
         <v>204</v>
       </c>
       <c r="N3" s="21" t="s">
         <v>205</v>
       </c>
-      <c r="O3" s="21" t="s">
+      <c r="O3" s="23" t="s">
         <v>206</v>
       </c>
       <c r="P3" s="21" t="s">
@@ -5138,725 +5695,803 @@
       <c r="W3" s="21" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="4" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X3" s="21" t="s">
+        <v>215</v>
+      </c>
+      <c r="Y3" s="21" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B4" s="24" t="s">
+        <v>218</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>219</v>
+      </c>
+      <c r="D4" s="24" t="s">
         <v>99</v>
       </c>
-      <c r="C4" s="24" t="s">
-        <v>216</v>
-      </c>
-      <c r="D4" s="24" t="s">
-        <v>217</v>
-      </c>
       <c r="E4" s="24" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F4" s="24" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="G4" s="24" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="H4" s="24" t="s">
-        <v>99</v>
+        <v>223</v>
       </c>
       <c r="I4" s="24" t="s">
         <v>220</v>
       </c>
       <c r="J4" s="24" t="s">
-        <v>221</v>
-      </c>
-      <c r="K4" s="25">
+        <v>99</v>
+      </c>
+      <c r="K4" s="24" t="s">
+        <v>224</v>
+      </c>
+      <c r="L4" s="24" t="s">
+        <v>225</v>
+      </c>
+      <c r="M4" s="26">
         <v>0.42857142857142855</v>
       </c>
-      <c r="L4" s="24" t="s">
-        <v>222</v>
-      </c>
-      <c r="M4" s="26">
+      <c r="N4" s="24" t="s">
+        <v>226</v>
+      </c>
+      <c r="O4" s="27">
         <v>4.8</v>
-      </c>
-      <c r="N4" s="24">
-        <v>0</v>
-      </c>
-      <c r="O4" s="24">
-        <v>0</v>
       </c>
       <c r="P4" s="24">
         <v>0</v>
       </c>
-      <c r="Q4" s="27" t="s">
-        <v>223</v>
-      </c>
-      <c r="R4" s="27" t="s">
-        <v>224</v>
-      </c>
-      <c r="S4" s="28"/>
-      <c r="T4" s="24"/>
-      <c r="U4" s="24" t="s">
-        <v>225</v>
-      </c>
+      <c r="Q4" s="24">
+        <v>0</v>
+      </c>
+      <c r="R4" s="24">
+        <v>0</v>
+      </c>
+      <c r="S4" s="25" t="s">
+        <v>227</v>
+      </c>
+      <c r="T4" s="25" t="s">
+        <v>228</v>
+      </c>
+      <c r="U4" s="28"/>
       <c r="V4" s="24"/>
-      <c r="W4" s="24"/>
-    </row>
-    <row r="5" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W4" s="24" t="s">
+        <v>229</v>
+      </c>
+      <c r="X4" s="24"/>
+      <c r="Y4" s="24"/>
+    </row>
+    <row r="5" ht="34" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B5" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>219</v>
+      </c>
+      <c r="D5" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="E5" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="F5" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="E5" s="14" t="s">
-        <v>227</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>228</v>
-      </c>
       <c r="G5" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="H5" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="I5" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="H5" s="14" t="s">
-        <v>229</v>
-      </c>
-      <c r="I5" s="14" t="s">
-        <v>230</v>
-      </c>
       <c r="J5" s="14" t="s">
-        <v>231</v>
-      </c>
-      <c r="K5" s="29">
+        <v>233</v>
+      </c>
+      <c r="K5" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="L5" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="M5" s="29">
         <v>0.5714285714285714</v>
       </c>
-      <c r="L5" s="14" t="s">
-        <v>232</v>
-      </c>
-      <c r="M5" s="30">
+      <c r="N5" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="O5" s="30">
         <v>4.7</v>
-      </c>
-      <c r="N5" s="14">
-        <v>0</v>
-      </c>
-      <c r="O5" s="14">
-        <v>0</v>
       </c>
       <c r="P5" s="14">
         <v>0</v>
       </c>
-      <c r="Q5" s="27" t="s">
+      <c r="Q5" s="14">
+        <v>0</v>
+      </c>
+      <c r="R5" s="14">
+        <v>0</v>
+      </c>
+      <c r="S5" s="25" t="s">
+        <v>227</v>
+      </c>
+      <c r="T5" s="25" t="s">
+        <v>228</v>
+      </c>
+      <c r="U5" s="28"/>
+      <c r="V5" s="14"/>
+      <c r="W5" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="X5" s="14"/>
+      <c r="Y5" s="14"/>
+    </row>
+    <row r="6" ht="34" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A6" s="24" t="s">
+        <v>237</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>218</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>219</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>220</v>
+      </c>
+      <c r="F6" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="G6" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="H6" s="24" t="s">
         <v>223</v>
       </c>
-      <c r="R5" s="27" t="s">
-        <v>224</v>
-      </c>
-      <c r="S5" s="28"/>
-      <c r="T5" s="14"/>
-      <c r="U5" s="14" t="s">
-        <v>225</v>
-      </c>
-      <c r="V5" s="14"/>
-      <c r="W5" s="14"/>
-    </row>
-    <row r="6" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A6" s="24" t="s">
-        <v>233</v>
-      </c>
-      <c r="B6" s="24" t="s">
+      <c r="I6" s="24" t="s">
+        <v>220</v>
+      </c>
+      <c r="J6" s="24" t="s">
         <v>99</v>
       </c>
-      <c r="C6" s="24" t="s">
-        <v>216</v>
-      </c>
-      <c r="D6" s="24" t="s">
-        <v>234</v>
-      </c>
-      <c r="E6" s="24" t="s">
-        <v>110</v>
-      </c>
-      <c r="F6" s="24" t="s">
-        <v>219</v>
-      </c>
-      <c r="G6" s="24" t="s">
-        <v>216</v>
-      </c>
-      <c r="H6" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="I6" s="24" t="s">
-        <v>235</v>
-      </c>
-      <c r="J6" s="24" t="s">
-        <v>236</v>
-      </c>
-      <c r="K6" s="25">
+      <c r="K6" s="24" t="s">
+        <v>239</v>
+      </c>
+      <c r="L6" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="M6" s="26">
         <v>0.42857142857142855</v>
       </c>
-      <c r="L6" s="24" t="s">
-        <v>222</v>
-      </c>
-      <c r="M6" s="26">
+      <c r="N6" s="24" t="s">
+        <v>226</v>
+      </c>
+      <c r="O6" s="27">
         <v>4.6</v>
-      </c>
-      <c r="N6" s="24">
-        <v>0</v>
-      </c>
-      <c r="O6" s="24">
-        <v>0</v>
       </c>
       <c r="P6" s="24">
         <v>0</v>
       </c>
-      <c r="Q6" s="27" t="s">
-        <v>223</v>
-      </c>
-      <c r="R6" s="27" t="s">
-        <v>224</v>
-      </c>
-      <c r="S6" s="28"/>
-      <c r="T6" s="24"/>
-      <c r="U6" s="24" t="s">
-        <v>225</v>
-      </c>
+      <c r="Q6" s="24">
+        <v>0</v>
+      </c>
+      <c r="R6" s="24">
+        <v>0</v>
+      </c>
+      <c r="S6" s="25" t="s">
+        <v>227</v>
+      </c>
+      <c r="T6" s="25" t="s">
+        <v>228</v>
+      </c>
+      <c r="U6" s="28"/>
       <c r="V6" s="24"/>
-      <c r="W6" s="24"/>
-    </row>
-    <row r="7" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W6" s="24" t="s">
+        <v>229</v>
+      </c>
+      <c r="X6" s="24"/>
+      <c r="Y6" s="24"/>
+    </row>
+    <row r="7" ht="34" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B7" s="14" t="s">
+        <v>242</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>243</v>
+      </c>
+      <c r="D7" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="C7" s="14" t="s">
-        <v>238</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>239</v>
-      </c>
       <c r="E7" s="14" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>244</v>
-      </c>
-      <c r="K7" s="29">
-        <v>0.5714285714285714</v>
+        <v>248</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>249</v>
       </c>
       <c r="L7" s="14" t="s">
-        <v>245</v>
-      </c>
-      <c r="M7" s="30">
+        <v>250</v>
+      </c>
+      <c r="M7" s="31">
+        <v>0.75</v>
+      </c>
+      <c r="N7" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="O7" s="30">
         <v>4.4</v>
-      </c>
-      <c r="N7" s="14">
-        <v>0</v>
-      </c>
-      <c r="O7" s="14">
-        <v>0</v>
       </c>
       <c r="P7" s="14">
         <v>0</v>
       </c>
-      <c r="Q7" s="27" t="s">
-        <v>223</v>
-      </c>
-      <c r="R7" s="27" t="s">
-        <v>224</v>
-      </c>
-      <c r="S7" s="28"/>
-      <c r="T7" s="14"/>
-      <c r="U7" s="14" t="s">
-        <v>225</v>
-      </c>
+      <c r="Q7" s="14">
+        <v>0</v>
+      </c>
+      <c r="R7" s="14">
+        <v>0</v>
+      </c>
+      <c r="S7" s="25" t="s">
+        <v>227</v>
+      </c>
+      <c r="T7" s="25" t="s">
+        <v>228</v>
+      </c>
+      <c r="U7" s="28"/>
       <c r="V7" s="14"/>
-      <c r="W7" s="14"/>
-    </row>
-    <row r="8" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W7" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="X7" s="14"/>
+      <c r="Y7" s="14"/>
+    </row>
+    <row r="8" ht="34" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" s="24" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B8" s="24" t="s">
+        <v>218</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>219</v>
+      </c>
+      <c r="D8" s="24" t="s">
         <v>99</v>
       </c>
-      <c r="C8" s="24" t="s">
-        <v>247</v>
-      </c>
-      <c r="D8" s="24" t="s">
-        <v>248</v>
-      </c>
       <c r="E8" s="24" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="F8" s="24" t="s">
-        <v>228</v>
+        <v>254</v>
       </c>
       <c r="G8" s="24" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="H8" s="24" t="s">
+        <v>232</v>
+      </c>
+      <c r="I8" s="24" t="s">
+        <v>253</v>
+      </c>
+      <c r="J8" s="24" t="s">
         <v>99</v>
       </c>
-      <c r="I8" s="24" t="s">
-        <v>250</v>
-      </c>
-      <c r="J8" s="24" t="s">
-        <v>251</v>
-      </c>
-      <c r="K8" s="29">
+      <c r="K8" s="24" t="s">
+        <v>256</v>
+      </c>
+      <c r="L8" s="24" t="s">
+        <v>257</v>
+      </c>
+      <c r="M8" s="29">
         <v>0.5714285714285714</v>
       </c>
-      <c r="L8" s="24" t="s">
-        <v>232</v>
-      </c>
-      <c r="M8" s="26">
+      <c r="N8" s="24" t="s">
+        <v>236</v>
+      </c>
+      <c r="O8" s="27">
         <v>4.3</v>
-      </c>
-      <c r="N8" s="24">
-        <v>0</v>
-      </c>
-      <c r="O8" s="24">
-        <v>0</v>
       </c>
       <c r="P8" s="24">
         <v>0</v>
       </c>
-      <c r="Q8" s="27" t="s">
-        <v>223</v>
-      </c>
-      <c r="R8" s="27" t="s">
-        <v>224</v>
-      </c>
-      <c r="S8" s="28"/>
-      <c r="T8" s="24"/>
-      <c r="U8" s="24" t="s">
-        <v>225</v>
-      </c>
+      <c r="Q8" s="24">
+        <v>0</v>
+      </c>
+      <c r="R8" s="24">
+        <v>0</v>
+      </c>
+      <c r="S8" s="25" t="s">
+        <v>227</v>
+      </c>
+      <c r="T8" s="25" t="s">
+        <v>228</v>
+      </c>
+      <c r="U8" s="28"/>
       <c r="V8" s="24"/>
-      <c r="W8" s="24"/>
-    </row>
-    <row r="9" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W8" s="24" t="s">
+        <v>229</v>
+      </c>
+      <c r="X8" s="24"/>
+      <c r="Y8" s="24"/>
+    </row>
+    <row r="9" ht="34" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>254</v>
+        <v>259</v>
+      </c>
+      <c r="C9" s="25" t="s">
+        <v>219</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="E9" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="G9" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="14" t="s">
-        <v>256</v>
-      </c>
-      <c r="G9" s="14" t="s">
-        <v>257</v>
-      </c>
       <c r="H9" s="14" t="s">
-        <v>253</v>
+        <v>219</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>259</v>
-      </c>
-      <c r="K9" s="31">
+        <v>260</v>
+      </c>
+      <c r="K9" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="L9" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="M9" s="31">
         <v>1</v>
       </c>
-      <c r="L9" s="14" t="s">
-        <v>260</v>
-      </c>
-      <c r="M9" s="30">
+      <c r="N9" s="14" t="s">
+        <v>266</v>
+      </c>
+      <c r="O9" s="30">
         <v>4.5</v>
-      </c>
-      <c r="N9" s="14">
-        <v>0</v>
-      </c>
-      <c r="O9" s="14">
-        <v>0</v>
       </c>
       <c r="P9" s="14">
         <v>0</v>
       </c>
-      <c r="Q9" s="27" t="s">
-        <v>261</v>
-      </c>
-      <c r="R9" s="27" t="s">
-        <v>262</v>
-      </c>
-      <c r="S9" s="28"/>
-      <c r="T9" s="14"/>
-      <c r="U9" s="14" t="s">
-        <v>225</v>
-      </c>
+      <c r="Q9" s="14">
+        <v>0</v>
+      </c>
+      <c r="R9" s="14">
+        <v>0</v>
+      </c>
+      <c r="S9" s="25" t="s">
+        <v>267</v>
+      </c>
+      <c r="T9" s="25" t="s">
+        <v>268</v>
+      </c>
+      <c r="U9" s="28"/>
       <c r="V9" s="14"/>
       <c r="W9" s="14" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="10" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+        <v>229</v>
+      </c>
+      <c r="X9" s="14"/>
+      <c r="Y9" s="14" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="24" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>253</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>265</v>
+        <v>259</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>271</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="F10" s="24" t="s">
-        <v>256</v>
+        <v>273</v>
       </c>
       <c r="G10" s="24" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="H10" s="24" t="s">
-        <v>253</v>
+        <v>219</v>
       </c>
       <c r="I10" s="24" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="J10" s="24" t="s">
-        <v>270</v>
-      </c>
-      <c r="K10" s="31">
+        <v>260</v>
+      </c>
+      <c r="K10" s="24" t="s">
+        <v>276</v>
+      </c>
+      <c r="L10" s="24" t="s">
+        <v>277</v>
+      </c>
+      <c r="M10" s="31">
         <v>0.75</v>
       </c>
-      <c r="L10" s="24" t="s">
-        <v>271</v>
-      </c>
-      <c r="M10" s="26">
+      <c r="N10" s="24" t="s">
+        <v>278</v>
+      </c>
+      <c r="O10" s="27">
         <v>4.5</v>
-      </c>
-      <c r="N10" s="24">
-        <v>0</v>
-      </c>
-      <c r="O10" s="24">
-        <v>0</v>
       </c>
       <c r="P10" s="24">
         <v>0</v>
       </c>
-      <c r="Q10" s="27" t="s">
-        <v>261</v>
-      </c>
-      <c r="R10" s="27" t="s">
-        <v>262</v>
-      </c>
-      <c r="S10" s="28"/>
-      <c r="T10" s="24"/>
-      <c r="U10" s="24" t="s">
-        <v>225</v>
-      </c>
+      <c r="Q10" s="24">
+        <v>0</v>
+      </c>
+      <c r="R10" s="24">
+        <v>0</v>
+      </c>
+      <c r="S10" s="25" t="s">
+        <v>267</v>
+      </c>
+      <c r="T10" s="25" t="s">
+        <v>268</v>
+      </c>
+      <c r="U10" s="28"/>
       <c r="V10" s="24"/>
       <c r="W10" s="24" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="11" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+        <v>229</v>
+      </c>
+      <c r="X10" s="24"/>
+      <c r="Y10" s="24" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="B11" s="14" t="s">
+        <v>242</v>
+      </c>
+      <c r="C11" s="25" t="s">
+        <v>243</v>
+      </c>
+      <c r="D11" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="C11" s="14" t="s">
-        <v>274</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>275</v>
-      </c>
       <c r="E11" s="14" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="H11" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="I11" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="J11" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="I11" s="14" t="s">
-        <v>279</v>
-      </c>
-      <c r="J11" s="14" t="s">
-        <v>280</v>
-      </c>
-      <c r="K11" s="25">
-        <v>0.2222222222222222</v>
+      <c r="K11" s="14" t="s">
+        <v>286</v>
       </c>
       <c r="L11" s="14" t="s">
-        <v>281</v>
-      </c>
-      <c r="M11" s="30">
+        <v>287</v>
+      </c>
+      <c r="M11" s="31">
+        <v>0.75</v>
+      </c>
+      <c r="N11" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="O11" s="30">
         <v>4.1</v>
-      </c>
-      <c r="N11" s="14">
-        <v>0</v>
-      </c>
-      <c r="O11" s="14">
-        <v>0</v>
       </c>
       <c r="P11" s="14">
         <v>0</v>
       </c>
-      <c r="Q11" s="27" t="s">
-        <v>261</v>
-      </c>
-      <c r="R11" s="27" t="s">
-        <v>262</v>
-      </c>
-      <c r="S11" s="28"/>
-      <c r="T11" s="14"/>
-      <c r="U11" s="14" t="s">
-        <v>225</v>
-      </c>
+      <c r="Q11" s="14">
+        <v>0</v>
+      </c>
+      <c r="R11" s="14">
+        <v>0</v>
+      </c>
+      <c r="S11" s="25" t="s">
+        <v>267</v>
+      </c>
+      <c r="T11" s="25" t="s">
+        <v>268</v>
+      </c>
+      <c r="U11" s="28"/>
       <c r="V11" s="14"/>
-      <c r="W11" s="14"/>
-    </row>
-    <row r="12" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W11" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="X11" s="14"/>
+      <c r="Y11" s="14"/>
+    </row>
+    <row r="12" ht="34" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12" s="24" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>283</v>
-      </c>
-      <c r="C12" s="24" t="s">
-        <v>284</v>
+        <v>242</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>243</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="F12" s="24" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="G12" s="24" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="H12" s="24" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="I12" s="24" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="J12" s="24" t="s">
-        <v>291</v>
-      </c>
-      <c r="K12" s="29">
-        <v>0.6</v>
+        <v>295</v>
+      </c>
+      <c r="K12" s="24" t="s">
+        <v>296</v>
       </c>
       <c r="L12" s="24" t="s">
-        <v>292</v>
-      </c>
-      <c r="M12" s="26">
+        <v>297</v>
+      </c>
+      <c r="M12" s="31">
+        <v>0.75</v>
+      </c>
+      <c r="N12" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="O12" s="27">
         <v>3.8</v>
-      </c>
-      <c r="N12" s="24">
-        <v>0</v>
-      </c>
-      <c r="O12" s="24">
-        <v>0</v>
       </c>
       <c r="P12" s="24">
         <v>0</v>
       </c>
-      <c r="Q12" s="27" t="s">
-        <v>261</v>
-      </c>
-      <c r="R12" s="27" t="s">
-        <v>262</v>
-      </c>
-      <c r="S12" s="28"/>
-      <c r="T12" s="24"/>
-      <c r="U12" s="24" t="s">
-        <v>225</v>
-      </c>
+      <c r="Q12" s="24">
+        <v>0</v>
+      </c>
+      <c r="R12" s="24">
+        <v>0</v>
+      </c>
+      <c r="S12" s="25" t="s">
+        <v>267</v>
+      </c>
+      <c r="T12" s="25" t="s">
+        <v>268</v>
+      </c>
+      <c r="U12" s="28"/>
       <c r="V12" s="24"/>
-      <c r="W12" s="24"/>
-    </row>
-    <row r="13" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W12" s="24" t="s">
+        <v>229</v>
+      </c>
+      <c r="X12" s="24"/>
+      <c r="Y12" s="24"/>
+    </row>
+    <row r="13" ht="34" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>283</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>294</v>
+        <v>242</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>243</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="H13" s="14" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="J13" s="14" t="s">
-        <v>300</v>
-      </c>
-      <c r="K13" s="29">
-        <v>0.5</v>
+        <v>303</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>304</v>
       </c>
       <c r="L13" s="14" t="s">
-        <v>301</v>
-      </c>
-      <c r="M13" s="30">
+        <v>305</v>
+      </c>
+      <c r="M13" s="31">
+        <v>1</v>
+      </c>
+      <c r="N13" s="14" t="s">
+        <v>306</v>
+      </c>
+      <c r="O13" s="30">
         <v>3.5</v>
-      </c>
-      <c r="N13" s="14">
-        <v>0</v>
-      </c>
-      <c r="O13" s="14">
-        <v>0</v>
       </c>
       <c r="P13" s="14">
         <v>0</v>
       </c>
-      <c r="Q13" s="27" t="s">
-        <v>261</v>
-      </c>
-      <c r="R13" s="27" t="s">
-        <v>262</v>
-      </c>
-      <c r="S13" s="28"/>
-      <c r="T13" s="14"/>
-      <c r="U13" s="14" t="s">
-        <v>302</v>
-      </c>
-      <c r="V13" s="14" t="s">
-        <v>303</v>
-      </c>
-      <c r="W13" s="14"/>
-    </row>
-    <row r="14" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Q13" s="14">
+        <v>0</v>
+      </c>
+      <c r="R13" s="14">
+        <v>0</v>
+      </c>
+      <c r="S13" s="25" t="s">
+        <v>267</v>
+      </c>
+      <c r="T13" s="25" t="s">
+        <v>268</v>
+      </c>
+      <c r="U13" s="28"/>
+      <c r="V13" s="14"/>
+      <c r="W13" s="14" t="s">
+        <v>307</v>
+      </c>
+      <c r="X13" s="14" t="s">
+        <v>308</v>
+      </c>
+      <c r="Y13" s="14"/>
+    </row>
+    <row r="14" ht="34" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" s="24" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>253</v>
-      </c>
-      <c r="C14" s="24" t="s">
-        <v>305</v>
+        <v>259</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>219</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>306</v>
+        <v>260</v>
       </c>
       <c r="E14" s="24" t="s">
+        <v>310</v>
+      </c>
+      <c r="F14" s="24" t="s">
+        <v>311</v>
+      </c>
+      <c r="G14" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="F14" s="24" t="s">
-        <v>307</v>
-      </c>
-      <c r="G14" s="24" t="s">
-        <v>308</v>
-      </c>
       <c r="H14" s="24" t="s">
-        <v>253</v>
+        <v>312</v>
       </c>
       <c r="I14" s="24" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="J14" s="24" t="s">
-        <v>310</v>
-      </c>
-      <c r="K14" s="31">
+        <v>260</v>
+      </c>
+      <c r="K14" s="24" t="s">
+        <v>314</v>
+      </c>
+      <c r="L14" s="24" t="s">
+        <v>315</v>
+      </c>
+      <c r="M14" s="31">
         <v>1</v>
       </c>
-      <c r="L14" s="24" t="s">
-        <v>260</v>
-      </c>
-      <c r="M14" s="26">
+      <c r="N14" s="24" t="s">
+        <v>266</v>
+      </c>
+      <c r="O14" s="27">
         <v>3.5</v>
-      </c>
-      <c r="N14" s="24">
-        <v>0</v>
-      </c>
-      <c r="O14" s="24">
-        <v>0</v>
       </c>
       <c r="P14" s="24">
         <v>0</v>
       </c>
-      <c r="Q14" s="27" t="s">
-        <v>261</v>
-      </c>
-      <c r="R14" s="27" t="s">
-        <v>262</v>
-      </c>
-      <c r="S14" s="28"/>
-      <c r="T14" s="24"/>
-      <c r="U14" s="24" t="s">
-        <v>225</v>
-      </c>
+      <c r="Q14" s="24">
+        <v>0</v>
+      </c>
+      <c r="R14" s="24">
+        <v>0</v>
+      </c>
+      <c r="S14" s="25" t="s">
+        <v>267</v>
+      </c>
+      <c r="T14" s="25" t="s">
+        <v>268</v>
+      </c>
+      <c r="U14" s="28"/>
       <c r="V14" s="24"/>
       <c r="W14" s="24" t="s">
-        <v>311</v>
+        <v>229</v>
+      </c>
+      <c r="X14" s="24"/>
+      <c r="Y14" s="24" t="s">
+        <v>316</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:W14"/>
+  <autoFilter ref="A3:Y14"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:W1"/>
-    <mergeCell ref="A2:W2"/>
+    <mergeCell ref="A1:Y1"/>
+    <mergeCell ref="A2:Y2"/>
   </mergeCells>
-  <dataValidations count="4">
-    <dataValidation type="list" sqref="Q10:Q14">
+  <dataValidations count="6">
+    <dataValidation type="list" sqref="C10:C14">
+      <formula1>"待核实,部分核实,已核实,团队诉求"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="C4:C14">
+      <formula1>"待核实,部分核实,已核实,团队诉求"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="S10:S14">
       <formula1>"待比较,备选,拟定,淘汰"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="Q4:Q14">
+    <dataValidation type="list" sqref="S4:S14">
       <formula1>"待比较,备选,拟定,淘汰"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="R10:R14">
+    <dataValidation type="list" sqref="T10:T14">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="R4:R14">
+    <dataValidation type="list" sqref="T4:T14">
       <formula1>"是,否"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5873,7 +6508,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -5884,15 +6519,16 @@
     <col min="7" max="7" width="36" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
     <col min="9" max="12" width="16" customWidth="1"/>
-    <col min="13" max="15" width="30" customWidth="1"/>
-    <col min="16" max="16" width="16" customWidth="1"/>
-    <col min="17" max="17" width="18" customWidth="1"/>
-    <col min="18" max="18" width="30" customWidth="1"/>
+    <col min="13" max="13" width="18" customWidth="1"/>
+    <col min="14" max="16" width="30" customWidth="1"/>
+    <col min="17" max="17" width="16" customWidth="1"/>
+    <col min="18" max="18" width="18" customWidth="1"/>
+    <col min="19" max="19" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" ht="36" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="32" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
@@ -5911,10 +6547,11 @@
       <c r="P1" s="32"/>
       <c r="Q1" s="32"/>
       <c r="R1" s="32"/>
-    </row>
-    <row r="2" ht="34" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S1" s="32"/>
+    </row>
+    <row r="2" ht="34" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="33" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="B2" s="33"/>
       <c r="C2" s="33"/>
@@ -5933,280 +6570,296 @@
       <c r="P2" s="33"/>
       <c r="Q2" s="33"/>
       <c r="R2" s="33"/>
-    </row>
-    <row r="3" ht="34" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S2" s="33"/>
+    </row>
+    <row r="3" ht="34" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
         <v>155</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="K3" s="21" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="L3" s="21" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="M3" s="21" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="N3" s="21" t="s">
-        <v>203</v>
+        <v>327</v>
       </c>
       <c r="O3" s="21" t="s">
-        <v>322</v>
+        <v>205</v>
       </c>
       <c r="P3" s="21" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="Q3" s="21" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="R3" s="21" t="s">
+        <v>330</v>
+      </c>
+      <c r="S3" s="21" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" ht="34" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="F4" s="24" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="G4" s="24"/>
       <c r="H4" s="24" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="I4" s="24" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="J4" s="24" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="K4" s="24" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="L4" s="24" t="s">
-        <v>331</v>
-      </c>
-      <c r="M4" s="24" t="s">
-        <v>332</v>
+        <v>337</v>
+      </c>
+      <c r="M4" s="24">
+        <v>1</v>
       </c>
       <c r="N4" s="24" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="O4" s="24" t="s">
-        <v>334</v>
+        <v>306</v>
       </c>
       <c r="P4" s="24" t="s">
-        <v>335</v>
-      </c>
-      <c r="Q4" s="24"/>
-      <c r="R4" s="24" t="s">
+        <v>339</v>
+      </c>
+      <c r="Q4" s="24" t="s">
+        <v>340</v>
+      </c>
+      <c r="R4" s="24"/>
+      <c r="S4" s="24" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>342</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>343</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>344</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>269</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>345</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>269</v>
+      </c>
+      <c r="H5" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="I5" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="J5" s="14" t="s">
+        <v>346</v>
+      </c>
+      <c r="K5" s="14" t="s">
         <v>336</v>
       </c>
-    </row>
-    <row r="5" ht="34" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
+      <c r="L5" s="14" t="s">
         <v>337</v>
       </c>
-      <c r="B5" s="14" t="s">
-        <v>225</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>338</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>339</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>263</v>
-      </c>
-      <c r="F5" s="14" t="s">
+      <c r="M5" s="14">
+        <v>1</v>
+      </c>
+      <c r="N5" s="14" t="s">
+        <v>347</v>
+      </c>
+      <c r="O5" s="14" t="s">
+        <v>266</v>
+      </c>
+      <c r="P5" s="14" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q5" s="14" t="s">
         <v>340</v>
       </c>
-      <c r="G5" s="14" t="s">
-        <v>263</v>
-      </c>
-      <c r="H5" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="I5" s="14" t="s">
-        <v>254</v>
-      </c>
-      <c r="J5" s="14" t="s">
-        <v>341</v>
-      </c>
-      <c r="K5" s="14" t="s">
-        <v>330</v>
-      </c>
-      <c r="L5" s="14" t="s">
-        <v>331</v>
-      </c>
-      <c r="M5" s="14" t="s">
-        <v>342</v>
-      </c>
-      <c r="N5" s="14" t="s">
+      <c r="R5" s="14"/>
+      <c r="S5" s="14"/>
+    </row>
+    <row r="6" ht="34" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" s="24" t="s">
+        <v>349</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>229</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>350</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>351</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>279</v>
+      </c>
+      <c r="F6" s="24" t="s">
+        <v>352</v>
+      </c>
+      <c r="G6" s="24" t="s">
+        <v>279</v>
+      </c>
+      <c r="H6" s="24" t="s">
         <v>260</v>
       </c>
-      <c r="O5" s="14" t="s">
-        <v>343</v>
-      </c>
-      <c r="P5" s="14" t="s">
-        <v>335</v>
-      </c>
-      <c r="Q5" s="14"/>
-      <c r="R5" s="14"/>
-    </row>
-    <row r="6" ht="34" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A6" s="24" t="s">
-        <v>344</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="C6" s="24" t="s">
-        <v>345</v>
-      </c>
-      <c r="D6" s="24" t="s">
+      <c r="I6" s="24" t="s">
+        <v>272</v>
+      </c>
+      <c r="J6" s="24" t="s">
         <v>346</v>
       </c>
-      <c r="E6" s="24" t="s">
-        <v>272</v>
-      </c>
-      <c r="F6" s="24" t="s">
+      <c r="K6" s="24" t="s">
+        <v>336</v>
+      </c>
+      <c r="L6" s="24" t="s">
+        <v>337</v>
+      </c>
+      <c r="M6" s="24">
+        <v>1</v>
+      </c>
+      <c r="N6" s="24" t="s">
+        <v>353</v>
+      </c>
+      <c r="O6" s="24" t="s">
+        <v>354</v>
+      </c>
+      <c r="P6" s="24" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q6" s="24" t="s">
+        <v>340</v>
+      </c>
+      <c r="R6" s="24"/>
+      <c r="S6" s="24" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>357</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>358</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>359</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>316</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>311</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>316</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="I7" s="14" t="s">
+        <v>310</v>
+      </c>
+      <c r="J7" s="14" t="s">
+        <v>346</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="L7" s="14" t="s">
+        <v>337</v>
+      </c>
+      <c r="M7" s="14">
+        <v>8</v>
+      </c>
+      <c r="N7" s="14" t="s">
         <v>347</v>
       </c>
-      <c r="G6" s="24" t="s">
-        <v>272</v>
-      </c>
-      <c r="H6" s="24" t="s">
-        <v>253</v>
-      </c>
-      <c r="I6" s="24" t="s">
-        <v>265</v>
-      </c>
-      <c r="J6" s="24" t="s">
-        <v>341</v>
-      </c>
-      <c r="K6" s="24" t="s">
-        <v>330</v>
-      </c>
-      <c r="L6" s="24" t="s">
-        <v>331</v>
-      </c>
-      <c r="M6" s="24" t="s">
-        <v>348</v>
-      </c>
-      <c r="N6" s="24" t="s">
-        <v>349</v>
-      </c>
-      <c r="O6" s="24" t="s">
-        <v>350</v>
-      </c>
-      <c r="P6" s="24" t="s">
-        <v>335</v>
-      </c>
-      <c r="Q6" s="24"/>
-      <c r="R6" s="24" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="7" ht="34" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
-        <v>352</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>225</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>353</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>354</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>311</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>306</v>
-      </c>
-      <c r="G7" s="14" t="s">
-        <v>311</v>
-      </c>
-      <c r="H7" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="I7" s="14" t="s">
-        <v>305</v>
-      </c>
-      <c r="J7" s="14" t="s">
-        <v>341</v>
-      </c>
-      <c r="K7" s="14" t="s">
-        <v>330</v>
-      </c>
-      <c r="L7" s="14" t="s">
-        <v>331</v>
-      </c>
-      <c r="M7" s="14" t="s">
-        <v>342</v>
-      </c>
-      <c r="N7" s="14" t="s">
-        <v>260</v>
-      </c>
       <c r="O7" s="14" t="s">
-        <v>355</v>
+        <v>266</v>
       </c>
       <c r="P7" s="14" t="s">
-        <v>356</v>
-      </c>
-      <c r="Q7" s="14"/>
-      <c r="R7" s="14" t="s">
-        <v>357</v>
+        <v>360</v>
+      </c>
+      <c r="Q7" s="14" t="s">
+        <v>361</v>
+      </c>
+      <c r="R7" s="14"/>
+      <c r="S7" s="14" t="s">
+        <v>362</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:R7"/>
+  <autoFilter ref="A3:S7"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:R1"/>
-    <mergeCell ref="A2:R2"/>
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A2:S2"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -6221,7 +6874,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -6231,15 +6884,16 @@
     <col min="5" max="5" width="38" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
     <col min="7" max="9" width="16" customWidth="1"/>
-    <col min="10" max="12" width="30" customWidth="1"/>
-    <col min="13" max="13" width="18" customWidth="1"/>
-    <col min="14" max="14" width="36" customWidth="1"/>
-    <col min="15" max="15" width="16" customWidth="1"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
+    <col min="11" max="13" width="30" customWidth="1"/>
+    <col min="14" max="14" width="18" customWidth="1"/>
+    <col min="15" max="15" width="36" customWidth="1"/>
+    <col min="16" max="16" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" ht="36" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="32" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
@@ -6255,10 +6909,11 @@
       <c r="M1" s="32"/>
       <c r="N1" s="32"/>
       <c r="O1" s="32"/>
-    </row>
-    <row r="2" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P1" s="32"/>
+    </row>
+    <row r="2" ht="34" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="33" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="B2" s="33"/>
       <c r="C2" s="33"/>
@@ -6274,231 +6929,247 @@
       <c r="M2" s="33"/>
       <c r="N2" s="33"/>
       <c r="O2" s="33"/>
-    </row>
-    <row r="3" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P2" s="33"/>
+    </row>
+    <row r="3" ht="34" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
         <v>155</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>360</v>
+        <v>326</v>
       </c>
       <c r="K3" s="21" t="s">
-        <v>321</v>
+        <v>365</v>
       </c>
       <c r="L3" s="21" t="s">
-        <v>203</v>
+        <v>327</v>
       </c>
       <c r="M3" s="21" t="s">
-        <v>324</v>
+        <v>205</v>
       </c>
       <c r="N3" s="21" t="s">
-        <v>214</v>
+        <v>330</v>
       </c>
       <c r="O3" s="21" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+      <c r="P3" s="21" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="F4" s="24" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="G4" s="24" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="H4" s="24" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="I4" s="24" t="s">
-        <v>330</v>
-      </c>
-      <c r="J4" s="24" t="s">
-        <v>362</v>
+        <v>336</v>
+      </c>
+      <c r="J4" s="24">
+        <v>1</v>
       </c>
       <c r="K4" s="24" t="s">
-        <v>332</v>
+        <v>367</v>
       </c>
       <c r="L4" s="24" t="s">
-        <v>333</v>
-      </c>
-      <c r="M4" s="24"/>
+        <v>338</v>
+      </c>
+      <c r="M4" s="24" t="s">
+        <v>306</v>
+      </c>
       <c r="N4" s="24"/>
-      <c r="O4" s="24" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="5" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O4" s="24"/>
+      <c r="P4" s="24" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="E5" s="14"/>
       <c r="F5" s="14" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>330</v>
-      </c>
-      <c r="J5" s="14" t="s">
-        <v>364</v>
+        <v>336</v>
+      </c>
+      <c r="J5" s="14">
+        <v>1</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>342</v>
+        <v>369</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>260</v>
-      </c>
-      <c r="M5" s="14"/>
-      <c r="N5" s="14" t="s">
-        <v>263</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="M5" s="14" t="s">
+        <v>266</v>
+      </c>
+      <c r="N5" s="14"/>
       <c r="O5" s="14" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="6" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+        <v>269</v>
+      </c>
+      <c r="P5" s="14" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="E6" s="24"/>
       <c r="F6" s="24" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="G6" s="24" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="H6" s="24" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="I6" s="24" t="s">
-        <v>330</v>
-      </c>
-      <c r="J6" s="24" t="s">
-        <v>366</v>
+        <v>336</v>
+      </c>
+      <c r="J6" s="24">
+        <v>1</v>
       </c>
       <c r="K6" s="24" t="s">
-        <v>348</v>
+        <v>371</v>
       </c>
       <c r="L6" s="24" t="s">
-        <v>349</v>
-      </c>
-      <c r="M6" s="24"/>
-      <c r="N6" s="24" t="s">
-        <v>272</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="M6" s="24" t="s">
+        <v>354</v>
+      </c>
+      <c r="N6" s="24"/>
       <c r="O6" s="24" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="7" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+      <c r="P6" s="24" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="E7" s="14"/>
       <c r="F7" s="14" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>330</v>
-      </c>
-      <c r="J7" s="14" t="s">
-        <v>364</v>
+        <v>336</v>
+      </c>
+      <c r="J7" s="14">
+        <v>8</v>
       </c>
       <c r="K7" s="14" t="s">
-        <v>342</v>
+        <v>369</v>
       </c>
       <c r="L7" s="14" t="s">
-        <v>260</v>
-      </c>
-      <c r="M7" s="14"/>
-      <c r="N7" s="14" t="s">
-        <v>311</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="M7" s="14" t="s">
+        <v>266</v>
+      </c>
+      <c r="N7" s="14"/>
       <c r="O7" s="14" t="s">
-        <v>368</v>
+        <v>316</v>
+      </c>
+      <c r="P7" s="14" t="s">
+        <v>373</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:O7"/>
+  <autoFilter ref="A3:P7"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A2:P2"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -6513,7 +7184,337 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AW4"/>
+  <dimension ref="A1:Q7"/>
+  <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="8" width="18" customWidth="1"/>
+    <col min="9" max="9" width="30" customWidth="1"/>
+    <col min="10" max="12" width="18" customWidth="1"/>
+    <col min="13" max="13" width="38" customWidth="1"/>
+    <col min="14" max="14" width="16" customWidth="1"/>
+    <col min="15" max="16" width="18" customWidth="1"/>
+    <col min="17" max="17" width="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A1" s="32" t="s">
+        <v>242</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+    </row>
+    <row r="2" ht="34" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" s="33" t="s">
+        <v>374</v>
+      </c>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33"/>
+      <c r="N2" s="33"/>
+      <c r="O2" s="33"/>
+      <c r="P2" s="33"/>
+      <c r="Q2" s="33"/>
+    </row>
+    <row r="3" ht="34" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>375</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>376</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>377</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>378</v>
+      </c>
+      <c r="H3" s="21" t="s">
+        <v>379</v>
+      </c>
+      <c r="I3" s="21" t="s">
+        <v>380</v>
+      </c>
+      <c r="J3" s="21" t="s">
+        <v>381</v>
+      </c>
+      <c r="K3" s="21" t="s">
+        <v>382</v>
+      </c>
+      <c r="L3" s="21" t="s">
+        <v>320</v>
+      </c>
+      <c r="M3" s="21" t="s">
+        <v>215</v>
+      </c>
+      <c r="N3" s="21" t="s">
+        <v>325</v>
+      </c>
+      <c r="O3" s="21" t="s">
+        <v>210</v>
+      </c>
+      <c r="P3" s="21" t="s">
+        <v>383</v>
+      </c>
+      <c r="Q3" s="21" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="24" t="s">
+        <v>298</v>
+      </c>
+      <c r="B4" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="C4" s="34" t="s">
+        <v>289</v>
+      </c>
+      <c r="D4" s="34" t="s">
+        <v>299</v>
+      </c>
+      <c r="E4" s="34" t="s">
+        <v>303</v>
+      </c>
+      <c r="F4" s="34" t="s">
+        <v>292</v>
+      </c>
+      <c r="G4" s="34" t="s">
+        <v>301</v>
+      </c>
+      <c r="H4" s="34" t="s">
+        <v>384</v>
+      </c>
+      <c r="I4" s="34" t="s">
+        <v>339</v>
+      </c>
+      <c r="J4" s="34" t="s">
+        <v>338</v>
+      </c>
+      <c r="K4" s="34" t="s">
+        <v>306</v>
+      </c>
+      <c r="L4" s="24" t="s">
+        <v>333</v>
+      </c>
+      <c r="M4" s="24" t="s">
+        <v>308</v>
+      </c>
+      <c r="N4" s="24" t="s">
+        <v>367</v>
+      </c>
+      <c r="O4" s="24" t="s">
+        <v>267</v>
+      </c>
+      <c r="P4" s="24" t="s">
+        <v>268</v>
+      </c>
+      <c r="Q4" s="24"/>
+    </row>
+    <row r="5" ht="34" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="B5" s="34" t="s">
+        <v>282</v>
+      </c>
+      <c r="C5" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="D5" s="34" t="s">
+        <v>281</v>
+      </c>
+      <c r="E5" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="F5" s="34" t="s">
+        <v>283</v>
+      </c>
+      <c r="G5" s="34" t="s">
+        <v>284</v>
+      </c>
+      <c r="H5" s="34" t="s">
+        <v>385</v>
+      </c>
+      <c r="I5" s="34" t="s">
+        <v>360</v>
+      </c>
+      <c r="J5" s="34" t="s">
+        <v>347</v>
+      </c>
+      <c r="K5" s="34" t="s">
+        <v>266</v>
+      </c>
+      <c r="L5" s="14" t="s">
+        <v>359</v>
+      </c>
+      <c r="M5" s="14"/>
+      <c r="N5" s="14" t="s">
+        <v>369</v>
+      </c>
+      <c r="O5" s="14" t="s">
+        <v>267</v>
+      </c>
+      <c r="P5" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="Q5" s="14"/>
+    </row>
+    <row r="6" ht="34" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" s="24" t="s">
+        <v>241</v>
+      </c>
+      <c r="B6" s="34" t="s">
+        <v>245</v>
+      </c>
+      <c r="C6" s="34" t="s">
+        <v>136</v>
+      </c>
+      <c r="D6" s="34" t="s">
+        <v>244</v>
+      </c>
+      <c r="E6" s="34" t="s">
+        <v>248</v>
+      </c>
+      <c r="F6" s="34" t="s">
+        <v>246</v>
+      </c>
+      <c r="G6" s="34" t="s">
+        <v>247</v>
+      </c>
+      <c r="H6" s="34" t="s">
+        <v>386</v>
+      </c>
+      <c r="I6" s="34" t="s">
+        <v>360</v>
+      </c>
+      <c r="J6" s="34" t="s">
+        <v>347</v>
+      </c>
+      <c r="K6" s="34" t="s">
+        <v>266</v>
+      </c>
+      <c r="L6" s="24" t="s">
+        <v>359</v>
+      </c>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24" t="s">
+        <v>369</v>
+      </c>
+      <c r="O6" s="24" t="s">
+        <v>227</v>
+      </c>
+      <c r="P6" s="24" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q6" s="24"/>
+    </row>
+    <row r="7" ht="34" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>288</v>
+      </c>
+      <c r="B7" s="34" t="s">
+        <v>291</v>
+      </c>
+      <c r="C7" s="34" t="s">
+        <v>289</v>
+      </c>
+      <c r="D7" s="34" t="s">
+        <v>290</v>
+      </c>
+      <c r="E7" s="34" t="s">
+        <v>295</v>
+      </c>
+      <c r="F7" s="34" t="s">
+        <v>292</v>
+      </c>
+      <c r="G7" s="34" t="s">
+        <v>293</v>
+      </c>
+      <c r="H7" s="34" t="s">
+        <v>387</v>
+      </c>
+      <c r="I7" s="34" t="s">
+        <v>360</v>
+      </c>
+      <c r="J7" s="34" t="s">
+        <v>347</v>
+      </c>
+      <c r="K7" s="34" t="s">
+        <v>266</v>
+      </c>
+      <c r="L7" s="14" t="s">
+        <v>359</v>
+      </c>
+      <c r="M7" s="14"/>
+      <c r="N7" s="14" t="s">
+        <v>369</v>
+      </c>
+      <c r="O7" s="14" t="s">
+        <v>267</v>
+      </c>
+      <c r="P7" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="Q7" s="14"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:Q7"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A2:Q2"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L扬州出行共创&amp;R第 &amp;P / &amp;N 页</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:AW3"/>
   <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -6524,7 +7525,7 @@
     <col min="6" max="6" width="18" customWidth="1"/>
     <col min="7" max="7" width="30" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="16" style="34" customWidth="1"/>
+    <col min="9" max="9" width="16" style="35" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
     <col min="11" max="11" width="16" customWidth="1"/>
     <col min="12" max="12" width="18" customWidth="1"/>
@@ -6558,7 +7559,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>369</v>
+        <v>388</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -6611,7 +7612,7 @@
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
@@ -6667,287 +7668,148 @@
         <v>155</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>371</v>
+        <v>390</v>
       </c>
       <c r="F3" s="21" t="s">
         <v>31</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>372</v>
+        <v>391</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>373</v>
-      </c>
-      <c r="I3" s="35" t="s">
-        <v>374</v>
+        <v>392</v>
+      </c>
+      <c r="I3" s="36" t="s">
+        <v>393</v>
       </c>
       <c r="J3" s="21" t="s">
         <v>40</v>
       </c>
       <c r="K3" s="21" t="s">
-        <v>375</v>
+        <v>394</v>
       </c>
       <c r="L3" s="21" t="s">
-        <v>376</v>
+        <v>395</v>
       </c>
       <c r="M3" s="21" t="s">
         <v>34</v>
       </c>
       <c r="N3" s="21" t="s">
-        <v>377</v>
+        <v>396</v>
       </c>
       <c r="O3" s="21" t="s">
-        <v>378</v>
+        <v>397</v>
       </c>
       <c r="P3" s="21" t="s">
-        <v>379</v>
+        <v>398</v>
       </c>
       <c r="Q3" s="21" t="s">
-        <v>380</v>
+        <v>399</v>
       </c>
       <c r="R3" s="21" t="s">
-        <v>381</v>
+        <v>400</v>
       </c>
       <c r="S3" s="21" t="s">
-        <v>382</v>
+        <v>401</v>
       </c>
       <c r="T3" s="21" t="s">
-        <v>383</v>
+        <v>402</v>
       </c>
       <c r="U3" s="21" t="s">
-        <v>384</v>
+        <v>403</v>
       </c>
       <c r="V3" s="21" t="s">
         <v>46</v>
       </c>
       <c r="W3" s="21" t="s">
-        <v>385</v>
+        <v>404</v>
       </c>
       <c r="X3" s="21" t="s">
         <v>91</v>
       </c>
       <c r="Y3" s="21" t="s">
-        <v>386</v>
+        <v>405</v>
       </c>
       <c r="Z3" s="21" t="s">
         <v>65</v>
       </c>
       <c r="AA3" s="21" t="s">
-        <v>387</v>
+        <v>406</v>
       </c>
       <c r="AB3" s="21" t="s">
-        <v>388</v>
+        <v>407</v>
       </c>
       <c r="AC3" s="21" t="s">
-        <v>389</v>
+        <v>408</v>
       </c>
       <c r="AD3" s="21" t="s">
-        <v>390</v>
+        <v>409</v>
       </c>
       <c r="AE3" s="21" t="s">
         <v>67</v>
       </c>
       <c r="AF3" s="21" t="s">
-        <v>391</v>
+        <v>410</v>
       </c>
       <c r="AG3" s="21" t="s">
-        <v>392</v>
+        <v>411</v>
       </c>
       <c r="AH3" s="23" t="s">
-        <v>393</v>
+        <v>412</v>
       </c>
       <c r="AI3" s="22" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AJ3" s="21" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AK3" s="21" t="s">
-        <v>394</v>
+        <v>413</v>
       </c>
       <c r="AL3" s="21" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AM3" s="21" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AN3" s="21" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO3" s="21" t="s">
-        <v>395</v>
+        <v>414</v>
       </c>
       <c r="AP3" s="21" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AQ3" s="21" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AR3" s="21" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AS3" s="21" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AT3" s="21" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AU3" s="21" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AV3" s="21" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AW3" s="21" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
-        <v>273</v>
-      </c>
-      <c r="B4" s="36" t="s">
-        <v>275</v>
-      </c>
-      <c r="C4" s="36" t="s">
-        <v>274</v>
-      </c>
-      <c r="D4" s="36" t="s">
-        <v>81</v>
-      </c>
-      <c r="E4" s="36" t="s">
-        <v>276</v>
-      </c>
-      <c r="F4" s="36" t="s">
-        <v>397</v>
-      </c>
-      <c r="G4" s="24" t="s">
-        <v>256</v>
-      </c>
-      <c r="H4" s="24" t="s">
-        <v>256</v>
-      </c>
-      <c r="I4" s="37">
-        <v>520</v>
-      </c>
-      <c r="J4" s="36" t="s">
-        <v>398</v>
-      </c>
-      <c r="K4" s="24" t="s">
-        <v>256</v>
-      </c>
-      <c r="L4" s="24" t="s">
-        <v>256</v>
-      </c>
-      <c r="M4" s="36" t="s">
-        <v>399</v>
-      </c>
-      <c r="N4" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="O4" s="36" t="s">
-        <v>278</v>
-      </c>
-      <c r="P4" s="36" t="s">
-        <v>400</v>
-      </c>
-      <c r="Q4" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="R4" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="S4" s="24" t="s">
-        <v>401</v>
-      </c>
-      <c r="T4" s="24" t="s">
-        <v>402</v>
-      </c>
-      <c r="U4" s="24" t="s">
-        <v>403</v>
-      </c>
-      <c r="V4" s="36" t="s">
-        <v>404</v>
-      </c>
-      <c r="W4" s="36" t="s">
-        <v>405</v>
-      </c>
-      <c r="X4" s="24" t="s">
-        <v>406</v>
-      </c>
-      <c r="Y4" s="24" t="s">
-        <v>256</v>
-      </c>
-      <c r="Z4" s="24" t="s">
-        <v>407</v>
-      </c>
-      <c r="AA4" s="24" t="s">
-        <v>408</v>
-      </c>
-      <c r="AB4" s="24" t="s">
-        <v>409</v>
-      </c>
-      <c r="AC4" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="AD4" s="24" t="s">
-        <v>410</v>
-      </c>
-      <c r="AE4" s="24" t="s">
-        <v>86</v>
-      </c>
-      <c r="AF4" s="24" t="s">
-        <v>279</v>
-      </c>
-      <c r="AG4" s="24" t="s">
-        <v>280</v>
-      </c>
-      <c r="AH4" s="26">
-        <v>4.1</v>
-      </c>
-      <c r="AI4" s="25">
-        <v>0.2222222222222222</v>
-      </c>
-      <c r="AJ4" s="24" t="s">
-        <v>281</v>
-      </c>
-      <c r="AK4" s="24" t="s">
-        <v>256</v>
-      </c>
-      <c r="AL4" s="24">
-        <v>0</v>
-      </c>
-      <c r="AM4" s="24">
-        <v>0</v>
-      </c>
-      <c r="AN4" s="24">
-        <v>0</v>
-      </c>
-      <c r="AO4" s="24"/>
-      <c r="AP4" s="27" t="s">
-        <v>261</v>
-      </c>
-      <c r="AQ4" s="27" t="s">
-        <v>262</v>
-      </c>
-      <c r="AR4" s="28"/>
-      <c r="AS4" s="24"/>
-      <c r="AT4" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="AU4" s="24"/>
-      <c r="AV4" s="24"/>
-      <c r="AW4" s="24" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
   </sheetData>
@@ -6956,14 +7818,6 @@
     <mergeCell ref="A1:AW1"/>
     <mergeCell ref="A2:AW2"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation type="list" sqref="AP4">
-      <formula1>"待比较,备选,拟定,淘汰"</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="AQ4">
-      <formula1>"是,否"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
@@ -6972,12 +7826,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AK4"/>
+  <dimension ref="A1:AK3"/>
   <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -6986,7 +7840,7 @@
     <col min="4" max="5" width="18" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="16" style="34" customWidth="1"/>
+    <col min="8" max="8" width="16" style="35" customWidth="1"/>
     <col min="9" max="13" width="18" customWidth="1"/>
     <col min="14" max="14" width="16" customWidth="1"/>
     <col min="15" max="15" width="18" customWidth="1"/>
@@ -7009,7 +7863,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -7050,7 +7904,7 @@
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
@@ -7094,215 +7948,112 @@
         <v>155</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>371</v>
+        <v>390</v>
       </c>
       <c r="G3" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="H3" s="35" t="s">
-        <v>415</v>
+      <c r="H3" s="36" t="s">
+        <v>419</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="K3" s="21" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="L3" s="21" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="M3" s="21" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="N3" s="21" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="O3" s="21" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="P3" s="21" t="s">
-        <v>389</v>
+        <v>408</v>
       </c>
       <c r="Q3" s="21" t="s">
-        <v>386</v>
+        <v>405</v>
       </c>
       <c r="R3" s="21" t="s">
-        <v>382</v>
+        <v>401</v>
       </c>
       <c r="S3" s="21" t="s">
         <v>67</v>
       </c>
       <c r="T3" s="21" t="s">
-        <v>391</v>
+        <v>410</v>
       </c>
       <c r="U3" s="21" t="s">
-        <v>392</v>
+        <v>411</v>
       </c>
       <c r="V3" s="23" t="s">
-        <v>393</v>
+        <v>412</v>
       </c>
       <c r="W3" s="22" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="X3" s="21" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Y3" s="21" t="s">
-        <v>394</v>
+        <v>413</v>
       </c>
       <c r="Z3" s="21" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AA3" s="21" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AB3" s="21" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AC3" s="21" t="s">
-        <v>395</v>
+        <v>414</v>
       </c>
       <c r="AD3" s="21" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AE3" s="21" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AF3" s="21" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AG3" s="21" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AH3" s="21" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AI3" s="21" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AJ3" s="21" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AK3" s="21" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
-        <v>237</v>
-      </c>
-      <c r="B4" s="36" t="s">
-        <v>239</v>
-      </c>
-      <c r="C4" s="36" t="s">
-        <v>238</v>
-      </c>
-      <c r="D4" s="36" t="s">
-        <v>242</v>
-      </c>
-      <c r="E4" s="36" t="s">
-        <v>92</v>
-      </c>
-      <c r="F4" s="36" t="s">
-        <v>240</v>
-      </c>
-      <c r="G4" s="36" t="s">
-        <v>423</v>
-      </c>
-      <c r="H4" s="37">
-        <v>80</v>
-      </c>
-      <c r="I4" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="J4" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="K4" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="L4" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="M4" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="N4" s="36" t="s">
-        <v>424</v>
-      </c>
-      <c r="O4" s="36" t="s">
-        <v>425</v>
-      </c>
-      <c r="P4" s="24" t="s">
-        <v>256</v>
-      </c>
-      <c r="Q4" s="24" t="s">
-        <v>256</v>
-      </c>
-      <c r="R4" s="24" t="s">
-        <v>256</v>
-      </c>
-      <c r="S4" s="24" t="s">
-        <v>86</v>
-      </c>
-      <c r="T4" s="24" t="s">
-        <v>243</v>
-      </c>
-      <c r="U4" s="24" t="s">
-        <v>244</v>
-      </c>
-      <c r="V4" s="26">
-        <v>4.4</v>
-      </c>
-      <c r="W4" s="29">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="X4" s="24" t="s">
-        <v>245</v>
-      </c>
-      <c r="Y4" s="24" t="s">
-        <v>256</v>
-      </c>
-      <c r="Z4" s="24">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="24">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="24"/>
-      <c r="AD4" s="27" t="s">
-        <v>223</v>
-      </c>
-      <c r="AE4" s="27" t="s">
-        <v>224</v>
-      </c>
-      <c r="AF4" s="28"/>
-      <c r="AG4" s="24"/>
-      <c r="AH4" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="AI4" s="24"/>
-      <c r="AJ4" s="24"/>
-      <c r="AK4" s="24" t="s">
-        <v>426</v>
+        <v>415</v>
       </c>
     </row>
   </sheetData>
@@ -7311,14 +8062,6 @@
     <mergeCell ref="A1:AK1"/>
     <mergeCell ref="A2:AK2"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation type="list" sqref="AD4">
-      <formula1>"待比较,备选,拟定,淘汰"</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="AE4">
-      <formula1>"是,否"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
@@ -7327,12 +8070,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AS5"/>
+  <dimension ref="A1:AS3"/>
   <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -7341,7 +8084,7 @@
     <col min="5" max="5" width="18" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="16" style="34" customWidth="1"/>
+    <col min="8" max="8" width="16" style="35" customWidth="1"/>
     <col min="9" max="11" width="18" customWidth="1"/>
     <col min="12" max="12" width="16" customWidth="1"/>
     <col min="13" max="13" width="18" customWidth="1"/>
@@ -7467,28 +8210,28 @@
         <v>155</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C3" s="21" t="s">
         <v>429</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>371</v>
+        <v>390</v>
       </c>
       <c r="G3" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="H3" s="35" t="s">
+      <c r="H3" s="36" t="s">
         <v>430</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="J3" s="21" t="s">
         <v>431</v>
@@ -7530,343 +8273,81 @@
         <v>443</v>
       </c>
       <c r="W3" s="21" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="X3" s="21" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="Y3" s="21" t="s">
-        <v>389</v>
+        <v>408</v>
       </c>
       <c r="Z3" s="21" t="s">
-        <v>386</v>
+        <v>405</v>
       </c>
       <c r="AA3" s="21" t="s">
         <v>67</v>
       </c>
       <c r="AB3" s="21" t="s">
-        <v>391</v>
+        <v>410</v>
       </c>
       <c r="AC3" s="21" t="s">
-        <v>392</v>
+        <v>411</v>
       </c>
       <c r="AD3" s="23" t="s">
-        <v>393</v>
+        <v>412</v>
       </c>
       <c r="AE3" s="22" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AF3" s="21" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AG3" s="21" t="s">
-        <v>394</v>
+        <v>413</v>
       </c>
       <c r="AH3" s="21" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AI3" s="21" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AJ3" s="21" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AK3" s="21" t="s">
-        <v>395</v>
+        <v>414</v>
       </c>
       <c r="AL3" s="21" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AM3" s="21" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AN3" s="21" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AO3" s="21" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AP3" s="21" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AQ3" s="21" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AR3" s="21" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AS3" s="21" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
-        <v>293</v>
-      </c>
-      <c r="B4" s="36" t="s">
-        <v>295</v>
-      </c>
-      <c r="C4" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="D4" s="36" t="s">
-        <v>294</v>
-      </c>
-      <c r="E4" s="36" t="s">
-        <v>298</v>
-      </c>
-      <c r="F4" s="36" t="s">
-        <v>286</v>
-      </c>
-      <c r="G4" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="H4" s="37">
-        <v>200</v>
-      </c>
-      <c r="I4" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="J4" s="36" t="s">
-        <v>444</v>
-      </c>
-      <c r="K4" s="36" t="s">
-        <v>445</v>
-      </c>
-      <c r="L4" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="M4" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="N4" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="O4" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="P4" s="24" t="s">
-        <v>256</v>
-      </c>
-      <c r="Q4" s="24" t="s">
-        <v>256</v>
-      </c>
-      <c r="R4" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="S4" s="36" t="s">
-        <v>446</v>
-      </c>
-      <c r="T4" s="36" t="s">
-        <v>224</v>
-      </c>
-      <c r="U4" s="24" t="s">
-        <v>256</v>
-      </c>
-      <c r="V4" s="24" t="s">
-        <v>256</v>
-      </c>
-      <c r="W4" s="24" t="s">
-        <v>256</v>
-      </c>
-      <c r="X4" s="24" t="s">
-        <v>447</v>
-      </c>
-      <c r="Y4" s="24" t="s">
-        <v>256</v>
-      </c>
-      <c r="Z4" s="24" t="s">
-        <v>256</v>
-      </c>
-      <c r="AA4" s="24" t="s">
-        <v>256</v>
-      </c>
-      <c r="AB4" s="24" t="s">
-        <v>448</v>
-      </c>
-      <c r="AC4" s="24" t="s">
-        <v>449</v>
-      </c>
-      <c r="AD4" s="26">
-        <v>3.5</v>
-      </c>
-      <c r="AE4" s="29">
-        <v>0.5</v>
-      </c>
-      <c r="AF4" s="24" t="s">
-        <v>301</v>
-      </c>
-      <c r="AG4" s="24" t="s">
-        <v>450</v>
-      </c>
-      <c r="AH4" s="24">
-        <v>0</v>
-      </c>
-      <c r="AI4" s="24">
-        <v>0</v>
-      </c>
-      <c r="AJ4" s="24">
-        <v>0</v>
-      </c>
-      <c r="AK4" s="24"/>
-      <c r="AL4" s="27" t="s">
-        <v>261</v>
-      </c>
-      <c r="AM4" s="27" t="s">
-        <v>262</v>
-      </c>
-      <c r="AN4" s="28"/>
-      <c r="AO4" s="24"/>
-      <c r="AP4" s="24" t="s">
-        <v>302</v>
-      </c>
-      <c r="AQ4" s="24" t="s">
-        <v>303</v>
-      </c>
-      <c r="AR4" s="24"/>
-      <c r="AS4" s="24" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="5" ht="34" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
-        <v>282</v>
-      </c>
-      <c r="B5" s="36" t="s">
-        <v>285</v>
-      </c>
-      <c r="C5" s="36" t="s">
-        <v>452</v>
-      </c>
-      <c r="D5" s="36" t="s">
-        <v>284</v>
-      </c>
-      <c r="E5" s="36" t="s">
-        <v>289</v>
-      </c>
-      <c r="F5" s="36" t="s">
-        <v>286</v>
-      </c>
-      <c r="G5" s="36" t="s">
-        <v>453</v>
-      </c>
-      <c r="H5" s="37"/>
-      <c r="I5" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="J5" s="36" t="s">
-        <v>454</v>
-      </c>
-      <c r="K5" s="36" t="s">
-        <v>455</v>
-      </c>
-      <c r="L5" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="M5" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="N5" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="O5" s="36" t="s">
-        <v>456</v>
-      </c>
-      <c r="P5" s="14" t="s">
-        <v>256</v>
-      </c>
-      <c r="Q5" s="14" t="s">
-        <v>256</v>
-      </c>
-      <c r="R5" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="S5" s="36" t="s">
-        <v>457</v>
-      </c>
-      <c r="T5" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="U5" s="14" t="s">
-        <v>256</v>
-      </c>
-      <c r="V5" s="14" t="s">
-        <v>256</v>
-      </c>
-      <c r="W5" s="14" t="s">
-        <v>256</v>
-      </c>
-      <c r="X5" s="14" t="s">
-        <v>458</v>
-      </c>
-      <c r="Y5" s="14" t="s">
-        <v>256</v>
-      </c>
-      <c r="Z5" s="14" t="s">
-        <v>256</v>
-      </c>
-      <c r="AA5" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="AB5" s="14" t="s">
-        <v>290</v>
-      </c>
-      <c r="AC5" s="14" t="s">
-        <v>291</v>
-      </c>
-      <c r="AD5" s="30">
-        <v>3.8</v>
-      </c>
-      <c r="AE5" s="29">
-        <v>0.6</v>
-      </c>
-      <c r="AF5" s="14" t="s">
-        <v>292</v>
-      </c>
-      <c r="AG5" s="14" t="s">
-        <v>256</v>
-      </c>
-      <c r="AH5" s="14">
-        <v>0</v>
-      </c>
-      <c r="AI5" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ5" s="14">
-        <v>0</v>
-      </c>
-      <c r="AK5" s="14"/>
-      <c r="AL5" s="27" t="s">
-        <v>261</v>
-      </c>
-      <c r="AM5" s="27" t="s">
-        <v>262</v>
-      </c>
-      <c r="AN5" s="28"/>
-      <c r="AO5" s="14"/>
-      <c r="AP5" s="14" t="s">
-        <v>225</v>
-      </c>
-      <c r="AQ5" s="14"/>
-      <c r="AR5" s="14"/>
-      <c r="AS5" s="14" t="s">
-        <v>459</v>
+        <v>415</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:AS5"/>
+  <autoFilter ref="A3:AS4"/>
   <mergeCells count="2">
     <mergeCell ref="A1:AS1"/>
     <mergeCell ref="A2:AS2"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation type="list" sqref="AL4:AL5">
-      <formula1>"待比较,备选,拟定,淘汰"</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="AM4:AM5">
-      <formula1>"是,否"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
@@ -7875,12 +8356,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AO4"/>
+  <dimension ref="A1:AO3"/>
   <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -7889,7 +8370,7 @@
     <col min="4" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="16" style="34" customWidth="1"/>
+    <col min="7" max="7" width="16" style="35" customWidth="1"/>
     <col min="8" max="10" width="18" customWidth="1"/>
     <col min="11" max="11" width="16" customWidth="1"/>
     <col min="12" max="13" width="18" customWidth="1"/>
@@ -7915,7 +8396,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>460</v>
+        <v>444</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -7960,7 +8441,7 @@
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
-        <v>461</v>
+        <v>445</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
@@ -8008,130 +8489,125 @@
         <v>155</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>371</v>
+        <v>390</v>
       </c>
       <c r="F3" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="G3" s="35" t="s">
-        <v>462</v>
+      <c r="G3" s="36" t="s">
+        <v>446</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>463</v>
+        <v>447</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>464</v>
+        <v>448</v>
       </c>
       <c r="K3" s="21" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="L3" s="21" t="s">
-        <v>465</v>
+        <v>449</v>
       </c>
       <c r="M3" s="21" t="s">
-        <v>466</v>
+        <v>450</v>
       </c>
       <c r="N3" s="21" t="s">
-        <v>467</v>
+        <v>451</v>
       </c>
       <c r="O3" s="21" t="s">
-        <v>468</v>
+        <v>452</v>
       </c>
       <c r="P3" s="21" t="s">
-        <v>469</v>
+        <v>453</v>
       </c>
       <c r="Q3" s="21" t="s">
         <v>34</v>
       </c>
       <c r="R3" s="21" t="s">
-        <v>470</v>
+        <v>454</v>
       </c>
       <c r="S3" s="21" t="s">
-        <v>382</v>
+        <v>401</v>
       </c>
       <c r="T3" s="21" t="s">
-        <v>386</v>
+        <v>405</v>
       </c>
       <c r="U3" s="21" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="V3" s="21" t="s">
-        <v>389</v>
+        <v>408</v>
       </c>
       <c r="W3" s="21" t="s">
         <v>67</v>
       </c>
       <c r="X3" s="21" t="s">
-        <v>391</v>
+        <v>410</v>
       </c>
       <c r="Y3" s="21" t="s">
-        <v>392</v>
+        <v>411</v>
       </c>
       <c r="Z3" s="23" t="s">
-        <v>393</v>
+        <v>412</v>
       </c>
       <c r="AA3" s="22" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AB3" s="21" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AC3" s="21" t="s">
-        <v>394</v>
+        <v>413</v>
       </c>
       <c r="AD3" s="21" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AE3" s="21" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AF3" s="21" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AG3" s="21" t="s">
-        <v>395</v>
+        <v>414</v>
       </c>
       <c r="AH3" s="21" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AI3" s="21" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AJ3" s="21" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AK3" s="21" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AL3" s="21" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AM3" s="21" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AN3" s="21" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AO3" s="21" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="4" spans="34:36" x14ac:dyDescent="0.25">
-      <c r="AH4" s="38"/>
-      <c r="AI4" s="38"/>
-      <c r="AJ4" s="39"/>
+        <v>415</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A3:AO4"/>
@@ -8139,621 +8615,6 @@
     <mergeCell ref="A1:AO1"/>
     <mergeCell ref="A2:AO2"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation type="list" sqref="AH4">
-      <formula1>"待比较,备选,拟定,淘汰"</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="AI4">
-      <formula1>"是,否"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
-  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
-  <headerFooter>
-    <oddFooter>&amp;L扬州出行共创&amp;R第 &amp;P / &amp;N 页</oddFooter>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:AH7"/>
-  <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
-  <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="18" style="34" customWidth="1"/>
-    <col min="8" max="8" width="30" customWidth="1"/>
-    <col min="9" max="9" width="16" customWidth="1"/>
-    <col min="10" max="13" width="18" customWidth="1"/>
-    <col min="14" max="14" width="30" customWidth="1"/>
-    <col min="15" max="16" width="16" customWidth="1"/>
-    <col min="17" max="18" width="18" customWidth="1"/>
-    <col min="19" max="19" width="16" style="18" customWidth="1"/>
-    <col min="20" max="20" width="18" style="17" customWidth="1"/>
-    <col min="21" max="22" width="30" customWidth="1"/>
-    <col min="23" max="28" width="18" customWidth="1"/>
-    <col min="29" max="29" width="30" customWidth="1"/>
-    <col min="30" max="30" width="18" customWidth="1"/>
-    <col min="31" max="31" width="16" customWidth="1"/>
-    <col min="32" max="32" width="38" customWidth="1"/>
-    <col min="33" max="33" width="36" customWidth="1"/>
-    <col min="34" max="34" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="36" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
-        <v>471</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="19"/>
-      <c r="P1" s="19"/>
-      <c r="Q1" s="19"/>
-      <c r="R1" s="19"/>
-      <c r="S1" s="19"/>
-      <c r="T1" s="19"/>
-      <c r="U1" s="19"/>
-      <c r="V1" s="19"/>
-      <c r="W1" s="19"/>
-      <c r="X1" s="19"/>
-      <c r="Y1" s="19"/>
-      <c r="Z1" s="19"/>
-      <c r="AA1" s="19"/>
-      <c r="AB1" s="19"/>
-      <c r="AC1" s="19"/>
-      <c r="AD1" s="19"/>
-      <c r="AE1" s="19"/>
-      <c r="AF1" s="19"/>
-      <c r="AG1" s="19"/>
-      <c r="AH1" s="19"/>
-    </row>
-    <row r="2" ht="34" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
-        <v>472</v>
-      </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
-      <c r="N2" s="20"/>
-      <c r="O2" s="20"/>
-      <c r="P2" s="20"/>
-      <c r="Q2" s="20"/>
-      <c r="R2" s="20"/>
-      <c r="S2" s="20"/>
-      <c r="T2" s="20"/>
-      <c r="U2" s="20"/>
-      <c r="V2" s="20"/>
-      <c r="W2" s="20"/>
-      <c r="X2" s="20"/>
-      <c r="Y2" s="20"/>
-      <c r="Z2" s="20"/>
-      <c r="AA2" s="20"/>
-      <c r="AB2" s="20"/>
-      <c r="AC2" s="20"/>
-      <c r="AD2" s="20"/>
-      <c r="AE2" s="20"/>
-      <c r="AF2" s="20"/>
-      <c r="AG2" s="20"/>
-      <c r="AH2" s="20"/>
-    </row>
-    <row r="3" ht="34" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="C3" s="21" t="s">
-        <v>194</v>
-      </c>
-      <c r="D3" s="21" t="s">
-        <v>199</v>
-      </c>
-      <c r="E3" s="21" t="s">
-        <v>371</v>
-      </c>
-      <c r="F3" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="G3" s="35" t="s">
-        <v>473</v>
-      </c>
-      <c r="H3" s="21" t="s">
-        <v>474</v>
-      </c>
-      <c r="I3" s="21" t="s">
-        <v>421</v>
-      </c>
-      <c r="J3" s="21" t="s">
-        <v>475</v>
-      </c>
-      <c r="K3" s="21" t="s">
-        <v>476</v>
-      </c>
-      <c r="L3" s="21" t="s">
-        <v>477</v>
-      </c>
-      <c r="M3" s="21" t="s">
-        <v>422</v>
-      </c>
-      <c r="N3" s="21" t="s">
-        <v>389</v>
-      </c>
-      <c r="O3" s="21" t="s">
-        <v>386</v>
-      </c>
-      <c r="P3" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q3" s="21" t="s">
-        <v>478</v>
-      </c>
-      <c r="R3" s="21" t="s">
-        <v>479</v>
-      </c>
-      <c r="S3" s="23" t="s">
-        <v>393</v>
-      </c>
-      <c r="T3" s="22" t="s">
-        <v>202</v>
-      </c>
-      <c r="U3" s="21" t="s">
-        <v>203</v>
-      </c>
-      <c r="V3" s="21" t="s">
-        <v>394</v>
-      </c>
-      <c r="W3" s="21" t="s">
-        <v>205</v>
-      </c>
-      <c r="X3" s="21" t="s">
-        <v>206</v>
-      </c>
-      <c r="Y3" s="21" t="s">
-        <v>207</v>
-      </c>
-      <c r="Z3" s="21" t="s">
-        <v>395</v>
-      </c>
-      <c r="AA3" s="21" t="s">
-        <v>208</v>
-      </c>
-      <c r="AB3" s="21" t="s">
-        <v>209</v>
-      </c>
-      <c r="AC3" s="21" t="s">
-        <v>210</v>
-      </c>
-      <c r="AD3" s="21" t="s">
-        <v>211</v>
-      </c>
-      <c r="AE3" s="21" t="s">
-        <v>212</v>
-      </c>
-      <c r="AF3" s="21" t="s">
-        <v>213</v>
-      </c>
-      <c r="AG3" s="21" t="s">
-        <v>214</v>
-      </c>
-      <c r="AH3" s="21" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="B4" s="36" t="s">
-        <v>217</v>
-      </c>
-      <c r="C4" s="36" t="s">
-        <v>216</v>
-      </c>
-      <c r="D4" s="36" t="s">
-        <v>99</v>
-      </c>
-      <c r="E4" s="36" t="s">
-        <v>218</v>
-      </c>
-      <c r="F4" s="36" t="s">
-        <v>218</v>
-      </c>
-      <c r="G4" s="37"/>
-      <c r="H4" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="I4" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="J4" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="K4" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="L4" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="M4" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="N4" s="24" t="s">
-        <v>256</v>
-      </c>
-      <c r="O4" s="24" t="s">
-        <v>256</v>
-      </c>
-      <c r="P4" s="24" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q4" s="24" t="s">
-        <v>220</v>
-      </c>
-      <c r="R4" s="24" t="s">
-        <v>221</v>
-      </c>
-      <c r="S4" s="26">
-        <v>4.8</v>
-      </c>
-      <c r="T4" s="25">
-        <v>0.42857142857142855</v>
-      </c>
-      <c r="U4" s="24" t="s">
-        <v>222</v>
-      </c>
-      <c r="V4" s="24" t="s">
-        <v>256</v>
-      </c>
-      <c r="W4" s="24">
-        <v>0</v>
-      </c>
-      <c r="X4" s="24">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="24">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="24"/>
-      <c r="AA4" s="27" t="s">
-        <v>223</v>
-      </c>
-      <c r="AB4" s="27" t="s">
-        <v>224</v>
-      </c>
-      <c r="AC4" s="28"/>
-      <c r="AD4" s="24"/>
-      <c r="AE4" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="AF4" s="24"/>
-      <c r="AG4" s="24"/>
-      <c r="AH4" s="24" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="5" ht="34" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
-        <v>246</v>
-      </c>
-      <c r="B5" s="36" t="s">
-        <v>248</v>
-      </c>
-      <c r="C5" s="36" t="s">
-        <v>247</v>
-      </c>
-      <c r="D5" s="36" t="s">
-        <v>99</v>
-      </c>
-      <c r="E5" s="36" t="s">
-        <v>249</v>
-      </c>
-      <c r="F5" s="36" t="s">
-        <v>249</v>
-      </c>
-      <c r="G5" s="37">
-        <v>0</v>
-      </c>
-      <c r="H5" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="I5" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="J5" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="K5" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="L5" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="M5" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="N5" s="14" t="s">
-        <v>256</v>
-      </c>
-      <c r="O5" s="14" t="s">
-        <v>256</v>
-      </c>
-      <c r="P5" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q5" s="14" t="s">
-        <v>250</v>
-      </c>
-      <c r="R5" s="14" t="s">
-        <v>251</v>
-      </c>
-      <c r="S5" s="30">
-        <v>4.3</v>
-      </c>
-      <c r="T5" s="29">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="U5" s="14" t="s">
-        <v>232</v>
-      </c>
-      <c r="V5" s="14" t="s">
-        <v>256</v>
-      </c>
-      <c r="W5" s="14">
-        <v>0</v>
-      </c>
-      <c r="X5" s="14">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="14">
-        <v>0</v>
-      </c>
-      <c r="Z5" s="14"/>
-      <c r="AA5" s="27" t="s">
-        <v>223</v>
-      </c>
-      <c r="AB5" s="27" t="s">
-        <v>224</v>
-      </c>
-      <c r="AC5" s="28"/>
-      <c r="AD5" s="14"/>
-      <c r="AE5" s="14" t="s">
-        <v>225</v>
-      </c>
-      <c r="AF5" s="14"/>
-      <c r="AG5" s="14"/>
-      <c r="AH5" s="14" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="6" ht="34" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A6" s="24" t="s">
-        <v>233</v>
-      </c>
-      <c r="B6" s="36" t="s">
-        <v>234</v>
-      </c>
-      <c r="C6" s="36" t="s">
-        <v>216</v>
-      </c>
-      <c r="D6" s="36" t="s">
-        <v>99</v>
-      </c>
-      <c r="E6" s="36" t="s">
-        <v>110</v>
-      </c>
-      <c r="F6" s="36" t="s">
-        <v>110</v>
-      </c>
-      <c r="G6" s="37"/>
-      <c r="H6" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="I6" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="J6" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="K6" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="L6" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="M6" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="N6" s="24" t="s">
-        <v>256</v>
-      </c>
-      <c r="O6" s="24" t="s">
-        <v>256</v>
-      </c>
-      <c r="P6" s="24" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q6" s="24" t="s">
-        <v>235</v>
-      </c>
-      <c r="R6" s="24" t="s">
-        <v>236</v>
-      </c>
-      <c r="S6" s="26">
-        <v>4.6</v>
-      </c>
-      <c r="T6" s="25">
-        <v>0.42857142857142855</v>
-      </c>
-      <c r="U6" s="24" t="s">
-        <v>222</v>
-      </c>
-      <c r="V6" s="24" t="s">
-        <v>256</v>
-      </c>
-      <c r="W6" s="24">
-        <v>0</v>
-      </c>
-      <c r="X6" s="24">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="24">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="24"/>
-      <c r="AA6" s="27" t="s">
-        <v>223</v>
-      </c>
-      <c r="AB6" s="27" t="s">
-        <v>224</v>
-      </c>
-      <c r="AC6" s="28"/>
-      <c r="AD6" s="24"/>
-      <c r="AE6" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="AF6" s="24"/>
-      <c r="AG6" s="24"/>
-      <c r="AH6" s="24" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="7" ht="34" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
-        <v>226</v>
-      </c>
-      <c r="B7" s="36" t="s">
-        <v>142</v>
-      </c>
-      <c r="C7" s="36" t="s">
-        <v>141</v>
-      </c>
-      <c r="D7" s="36" t="s">
-        <v>229</v>
-      </c>
-      <c r="E7" s="36" t="s">
-        <v>227</v>
-      </c>
-      <c r="F7" s="36" t="s">
-        <v>227</v>
-      </c>
-      <c r="G7" s="37">
-        <v>0</v>
-      </c>
-      <c r="H7" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="I7" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="J7" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="K7" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="L7" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="M7" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="N7" s="14" t="s">
-        <v>256</v>
-      </c>
-      <c r="O7" s="14" t="s">
-        <v>256</v>
-      </c>
-      <c r="P7" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q7" s="14" t="s">
-        <v>230</v>
-      </c>
-      <c r="R7" s="14" t="s">
-        <v>231</v>
-      </c>
-      <c r="S7" s="30">
-        <v>4.7</v>
-      </c>
-      <c r="T7" s="29">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="U7" s="14" t="s">
-        <v>232</v>
-      </c>
-      <c r="V7" s="14" t="s">
-        <v>256</v>
-      </c>
-      <c r="W7" s="14">
-        <v>0</v>
-      </c>
-      <c r="X7" s="14">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="14">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="14"/>
-      <c r="AA7" s="27" t="s">
-        <v>223</v>
-      </c>
-      <c r="AB7" s="27" t="s">
-        <v>224</v>
-      </c>
-      <c r="AC7" s="28"/>
-      <c r="AD7" s="14"/>
-      <c r="AE7" s="14" t="s">
-        <v>225</v>
-      </c>
-      <c r="AF7" s="14"/>
-      <c r="AG7" s="14"/>
-      <c r="AH7" s="14" t="s">
-        <v>481</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A3:AH7"/>
-  <mergeCells count="2">
-    <mergeCell ref="A1:AH1"/>
-    <mergeCell ref="A2:AH2"/>
-  </mergeCells>
-  <dataValidations count="2">
-    <dataValidation type="list" sqref="AA4:AA7">
-      <formula1>"待比较,备选,拟定,淘汰"</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="AB4:AB7">
-      <formula1>"是,否"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
